--- a/artfynd/A 56618-2025 artfynd.xlsx
+++ b/artfynd/A 56618-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130043006</v>
+        <v>130042984</v>
       </c>
       <c r="B2" t="n">
-        <v>91601</v>
+        <v>91606</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1108</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>442805</v>
+        <v>442318</v>
       </c>
       <c r="R2" t="n">
-        <v>7006065</v>
+        <v>7005873</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,12 +755,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>På död gammal gran</t>
+          <t>På gammal granlåga</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130042984</v>
+        <v>130042928</v>
       </c>
       <c r="B3" t="n">
-        <v>91605</v>
+        <v>78503</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -798,21 +798,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>502</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Ladlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Calicium tigillare</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Pers.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>442318</v>
+        <v>442500</v>
       </c>
       <c r="R3" t="n">
-        <v>7005873</v>
+        <v>7005787</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,7 +857,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -867,12 +867,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>På gammal granlåga</t>
+          <t>På ved på gammal barrhögstubbe i gammal granskog</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,22 +887,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Ulrika Nordin, Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130042928</v>
+        <v>130043006</v>
       </c>
       <c r="B4" t="n">
-        <v>78502</v>
+        <v>91602</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -910,21 +910,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>502</v>
+        <v>1108</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ladlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Calicium tigillare</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Pers.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -934,10 +934,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>442500</v>
+        <v>442805</v>
       </c>
       <c r="R4" t="n">
-        <v>7005787</v>
+        <v>7006065</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,7 +969,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -979,12 +979,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>På ved på gammal barrhögstubbe i gammal granskog</t>
+          <t>På död gammal gran</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -999,12 +999,12 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Ulrika Nordin, Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1233,7 +1233,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Ulrika Nordin, Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1350,17 +1350,17 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Ulrika Nordin, Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130042955</v>
+        <v>130043004</v>
       </c>
       <c r="B8" t="n">
-        <v>79087</v>
+        <v>91602</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1368,21 +1368,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1392,10 +1392,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>442534</v>
+        <v>442160</v>
       </c>
       <c r="R8" t="n">
-        <v>7005878</v>
+        <v>7005610</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1427,7 +1427,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1437,12 +1437,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>På gran, 40 cm diameter</t>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1457,22 +1457,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Ulrika Nordin, Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Ulrika Nordin, Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130043004</v>
+        <v>130043003</v>
       </c>
       <c r="B9" t="n">
-        <v>91601</v>
+        <v>78100</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1480,21 +1480,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1108</v>
+        <v>228579</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1504,10 +1504,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>442160</v>
+        <v>442219</v>
       </c>
       <c r="R9" t="n">
-        <v>7005610</v>
+        <v>7005641</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1539,7 +1539,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1549,12 +1549,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>På gran</t>
+          <t>på gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1574,17 +1574,17 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Ulrika Nordin, Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130043003</v>
+        <v>130042955</v>
       </c>
       <c r="B10" t="n">
-        <v>78100</v>
+        <v>79088</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1592,21 +1592,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1616,10 +1616,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>442219</v>
+        <v>442534</v>
       </c>
       <c r="R10" t="n">
-        <v>7005641</v>
+        <v>7005878</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1651,7 +1651,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1661,12 +1661,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>på gammal gran i gammal granskog</t>
+          <t>På gran, 40 cm diameter</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1681,12 +1681,12 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Ulrika Nordin, Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
@@ -1696,7 +1696,7 @@
         <v>130042992</v>
       </c>
       <c r="B11" t="n">
-        <v>92323</v>
+        <v>92324</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1798,7 +1798,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Ulrika Nordin, Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
@@ -1808,7 +1808,7 @@
         <v>130042927</v>
       </c>
       <c r="B12" t="n">
-        <v>80192</v>
+        <v>80193</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1910,17 +1910,17 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Ulrika Nordin, Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130042946</v>
+        <v>130042985</v>
       </c>
       <c r="B13" t="n">
-        <v>79087</v>
+        <v>91606</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1928,21 +1928,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1952,10 +1952,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>442870</v>
+        <v>442272</v>
       </c>
       <c r="R13" t="n">
-        <v>7006117</v>
+        <v>7005748</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1987,7 +1987,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1997,12 +1997,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>på granlåga</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2017,22 +2017,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130042980</v>
+        <v>130042946</v>
       </c>
       <c r="B14" t="n">
-        <v>83058</v>
+        <v>79088</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2040,21 +2040,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2064,10 +2064,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>442510</v>
+        <v>442870</v>
       </c>
       <c r="R14" t="n">
-        <v>7005835</v>
+        <v>7006117</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2099,7 +2099,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2109,7 +2109,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
@@ -2129,22 +2129,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130042985</v>
+        <v>130042980</v>
       </c>
       <c r="B15" t="n">
-        <v>91605</v>
+        <v>83059</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2152,21 +2152,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>6440</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2176,10 +2176,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>442272</v>
+        <v>442510</v>
       </c>
       <c r="R15" t="n">
-        <v>7005748</v>
+        <v>7005835</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2211,7 +2211,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2221,12 +2221,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>på granlåga</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2256,7 +2256,7 @@
         <v>130042923</v>
       </c>
       <c r="B16" t="n">
-        <v>83053</v>
+        <v>83054</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2358,17 +2358,17 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Ulrika Nordin, Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130042996</v>
+        <v>130042932</v>
       </c>
       <c r="B17" t="n">
-        <v>57740</v>
+        <v>91602</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2376,39 +2376,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Skog mellan Stenmyren och Frossjöbodarna, väster om Ågårdarna, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>442156</v>
+        <v>442535</v>
       </c>
       <c r="R17" t="n">
-        <v>7005705</v>
+        <v>7005862</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2440,7 +2435,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2450,12 +2445,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Färska och äldre ringhack på gran</t>
+          <t>På granhögstubbe i gammal granskog</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2470,12 +2465,12 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Ulrika Nordin, Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
@@ -2485,7 +2480,7 @@
         <v>130042952</v>
       </c>
       <c r="B18" t="n">
-        <v>83058</v>
+        <v>83059</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2594,10 +2589,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130042932</v>
+        <v>130042996</v>
       </c>
       <c r="B19" t="n">
-        <v>91601</v>
+        <v>57740</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2605,34 +2600,39 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Skog mellan Stenmyren och Frossjöbodarna, väster om Ågårdarna, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>442535</v>
+        <v>442156</v>
       </c>
       <c r="R19" t="n">
-        <v>7005862</v>
+        <v>7005705</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2664,7 +2664,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2674,12 +2674,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>På granhögstubbe i gammal granskog</t>
+          <t>Färska och äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2694,22 +2694,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Ulrika Nordin, Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130042960</v>
+        <v>130042916</v>
       </c>
       <c r="B20" t="n">
-        <v>78100</v>
+        <v>91606</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2717,21 +2717,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>228579</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2741,10 +2741,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>442328</v>
+        <v>442264</v>
       </c>
       <c r="R20" t="n">
-        <v>7005788</v>
+        <v>7005760</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2776,7 +2776,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2786,12 +2786,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>På gammal gran ca 30 cm i diameter</t>
+          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2806,7 +2806,7 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
@@ -2818,10 +2818,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130042916</v>
+        <v>130042960</v>
       </c>
       <c r="B21" t="n">
-        <v>91605</v>
+        <v>78100</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2829,21 +2829,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>228579</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2853,10 +2853,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>442264</v>
+        <v>442328</v>
       </c>
       <c r="R21" t="n">
-        <v>7005760</v>
+        <v>7005788</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2888,7 +2888,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2898,12 +2898,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>På granlåga</t>
+          <t>På gammal gran ca 30 cm i diameter</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2918,42 +2918,46 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Ulrika Nordin, Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130042934</v>
+        <v>130042956</v>
       </c>
       <c r="B22" t="n">
-        <v>91625</v>
+        <v>83057</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5432</v>
+        <v>6486</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skuggnål</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr"/>
+          <t>Chaenotheca sphaerocephala</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Nádv.</t>
+        </is>
+      </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2961,10 +2965,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>442211</v>
+        <v>442534</v>
       </c>
       <c r="R22" t="n">
-        <v>7005732</v>
+        <v>7005878</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2996,7 +3000,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3006,12 +3010,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>Vid basen av gran ca 40 cm i diameter</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3026,12 +3030,12 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Ulrika Nordin, Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
@@ -3041,7 +3045,7 @@
         <v>130042988</v>
       </c>
       <c r="B23" t="n">
-        <v>91605</v>
+        <v>91606</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3143,39 +3147,39 @@
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Ulrika Nordin, Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130042929</v>
+        <v>130042987</v>
       </c>
       <c r="B24" t="n">
-        <v>97668</v>
+        <v>91606</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>221945</v>
+        <v>1202</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3185,10 +3189,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>442265</v>
+        <v>442685</v>
       </c>
       <c r="R24" t="n">
-        <v>7005695</v>
+        <v>7005938</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3220,7 +3224,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3230,12 +3234,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>På marken i gammal granskog</t>
+          <t>på granlåga</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3250,12 +3254,12 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Ulrika Nordin, Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
@@ -3265,7 +3269,7 @@
         <v>130042981</v>
       </c>
       <c r="B25" t="n">
-        <v>83058</v>
+        <v>83059</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3374,10 +3378,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130042987</v>
+        <v>130042934</v>
       </c>
       <c r="B26" t="n">
-        <v>91605</v>
+        <v>91626</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3385,23 +3389,19 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3409,10 +3409,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>442685</v>
+        <v>442211</v>
       </c>
       <c r="R26" t="n">
-        <v>7005938</v>
+        <v>7005732</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3444,7 +3444,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3454,12 +3454,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>på granlåga</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3474,57 +3474,62 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Ulrika Nordin, Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130042956</v>
+        <v>130042954</v>
       </c>
       <c r="B27" t="n">
-        <v>83056</v>
+        <v>57740</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6486</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Skuggnål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Chaenotheca sphaerocephala</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Skog mellan Stenmyren och Frossjöbodarna, väster om Ågårdarna, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>442534</v>
+        <v>442278</v>
       </c>
       <c r="R27" t="n">
-        <v>7005878</v>
+        <v>7005808</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3556,7 +3561,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3566,12 +3571,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Vid basen av gran ca 40 cm i diameter</t>
+          <t>Rikligt med färska ringhack på gran ca 40 cm i diameter</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3598,50 +3603,45 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130042954</v>
+        <v>130042929</v>
       </c>
       <c r="B28" t="n">
-        <v>57740</v>
+        <v>97669</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Skog mellan Stenmyren och Frossjöbodarna, väster om Ågårdarna, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>442278</v>
+        <v>442265</v>
       </c>
       <c r="R28" t="n">
-        <v>7005808</v>
+        <v>7005695</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3673,7 +3673,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3683,12 +3683,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Rikligt med färska ringhack på gran ca 40 cm i diameter</t>
+          <t>På marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3703,7 +3703,7 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
@@ -3715,32 +3715,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130042922</v>
+        <v>130043005</v>
       </c>
       <c r="B29" t="n">
-        <v>75071</v>
+        <v>91602</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6428</v>
+        <v>1108</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3750,10 +3750,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>442311</v>
+        <v>442514</v>
       </c>
       <c r="R29" t="n">
-        <v>7005788</v>
+        <v>7005889</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3785,7 +3785,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3795,12 +3795,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>På ved på gammal avverkningsstubbe under grov gammal gran</t>
+          <t>På granhögstubbe</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3815,22 +3815,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Ulrika Nordin, Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130043005</v>
+        <v>130042953</v>
       </c>
       <c r="B30" t="n">
-        <v>91601</v>
+        <v>78111</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3838,21 +3838,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1108</v>
+        <v>314</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Vitskaftad svartspik</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Chaenothecopsis viridialba</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Kremp.) A.F.W.Schmidt</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3862,10 +3862,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>442514</v>
+        <v>442818</v>
       </c>
       <c r="R30" t="n">
-        <v>7005889</v>
+        <v>7006070</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3897,7 +3897,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>På granhögstubbe</t>
+          <t>På gammal gran ca 25 cm i diameter</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3921,68 +3921,64 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Ulrika Nordin, Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130042917</v>
+        <v>130042922</v>
       </c>
       <c r="B31" t="n">
-        <v>57740</v>
+        <v>75071</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>6428</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Skog mellan Stenmyren och Frossjöbodarna, väster om Ågårdarna, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>442320</v>
+        <v>442311</v>
       </c>
       <c r="R31" t="n">
-        <v>7005822</v>
+        <v>7005788</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4014,7 +4010,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4024,12 +4020,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Rikligt med ringhack på 55 cm grov gammal gran</t>
+          <t>På ved på gammal avverkningsstubbe under grov gammal gran</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4049,17 +4045,17 @@
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Ulrika Nordin, Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130042953</v>
+        <v>130042917</v>
       </c>
       <c r="B32" t="n">
-        <v>78111</v>
+        <v>57740</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4067,34 +4063,39 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>314</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vitskaftad svartspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Chaenothecopsis viridialba</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Kremp.) A.F.W.Schmidt</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Skog mellan Stenmyren och Frossjöbodarna, väster om Ågårdarna, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>442818</v>
+        <v>442320</v>
       </c>
       <c r="R32" t="n">
-        <v>7006070</v>
+        <v>7005822</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4126,7 +4127,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4136,12 +4137,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>På gammal gran ca 25 cm i diameter</t>
+          <t>Rikligt med ringhack på 55 cm grov gammal gran</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4150,14 +4151,13 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
@@ -4172,7 +4172,7 @@
         <v>130043007</v>
       </c>
       <c r="B33" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4274,7 +4274,7 @@
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Ulrika Nordin, Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
@@ -4284,7 +4284,7 @@
         <v>130042937</v>
       </c>
       <c r="B34" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Ulrika Nordin, Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
@@ -4619,7 +4619,7 @@
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Ulrika Nordin, Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
@@ -4629,7 +4629,7 @@
         <v>130042942</v>
       </c>
       <c r="B37" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4738,10 +4738,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>130042935</v>
+        <v>130043001</v>
       </c>
       <c r="B38" t="n">
-        <v>91625</v>
+        <v>83064</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4749,19 +4749,23 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5432</v>
+        <v>1467</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr"/>
+          <t>Sclerophora coniophaea</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+        </is>
+      </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
@@ -4769,10 +4773,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>442524</v>
+        <v>442691</v>
       </c>
       <c r="R38" t="n">
-        <v>7005879</v>
+        <v>7005901</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4804,7 +4808,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4814,12 +4818,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>På död gran i gammal granskog</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4834,22 +4838,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Ulrika Nordin, Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>130042995</v>
+        <v>130042961</v>
       </c>
       <c r="B39" t="n">
-        <v>57740</v>
+        <v>91626</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4857,39 +4861,30 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr"/>
       <c r="I39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Skog mellan Stenmyren och Frossjöbodarna, väster om Ågårdarna, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>442161</v>
+        <v>442177</v>
       </c>
       <c r="R39" t="n">
-        <v>7005744</v>
+        <v>7005633</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4921,7 +4916,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4931,12 +4926,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>På död gran ca 37 cm i diameter</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4951,22 +4946,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Ulrika Nordin, Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>130042961</v>
+        <v>130042935</v>
       </c>
       <c r="B40" t="n">
-        <v>91625</v>
+        <v>91626</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4994,10 +4989,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>442177</v>
+        <v>442524</v>
       </c>
       <c r="R40" t="n">
-        <v>7005633</v>
+        <v>7005879</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5029,7 +5024,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5039,12 +5034,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>På död gran ca 37 cm i diameter</t>
+          <t>På död gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5059,22 +5054,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Ulrika Nordin, Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>130043001</v>
+        <v>130042995</v>
       </c>
       <c r="B41" t="n">
-        <v>83063</v>
+        <v>57740</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5082,34 +5077,39 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1467</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Skog mellan Stenmyren och Frossjöbodarna, väster om Ågårdarna, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>442691</v>
+        <v>442161</v>
       </c>
       <c r="R41" t="n">
-        <v>7005901</v>
+        <v>7005744</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5141,7 +5141,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5176,39 +5176,39 @@
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Ulrika Nordin, Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>130042940</v>
+        <v>130042982</v>
       </c>
       <c r="B42" t="n">
-        <v>98701</v>
+        <v>83059</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220093</v>
+        <v>6440</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5218,10 +5218,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>442223</v>
+        <v>442693</v>
       </c>
       <c r="R42" t="n">
-        <v>7005661</v>
+        <v>7005900</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5253,7 +5253,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5263,12 +5263,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>På marken i gammal granskog</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5283,12 +5283,12 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
@@ -5298,7 +5298,7 @@
         <v>130042959</v>
       </c>
       <c r="B43" t="n">
-        <v>83058</v>
+        <v>83059</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5407,32 +5407,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>130042982</v>
+        <v>130042940</v>
       </c>
       <c r="B44" t="n">
-        <v>83058</v>
+        <v>98702</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6440</v>
+        <v>220093</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5442,10 +5442,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>442693</v>
+        <v>442223</v>
       </c>
       <c r="R44" t="n">
-        <v>7005900</v>
+        <v>7005661</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5477,7 +5477,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5487,12 +5487,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>På marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5507,22 +5507,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>130042924</v>
+        <v>130042986</v>
       </c>
       <c r="B45" t="n">
-        <v>83063</v>
+        <v>91606</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5530,21 +5530,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1467</v>
+        <v>1202</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5554,10 +5554,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>442311</v>
+        <v>442272</v>
       </c>
       <c r="R45" t="n">
-        <v>7005788</v>
+        <v>7005763</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5589,7 +5589,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5599,12 +5599,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>På bark vid basen av gammal levande grov gran, även nordlig nållav och rostfläck och Chaenothecopsis vainioana på avverkningsstubbe under granen</t>
+          <t>på granlåga</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5619,22 +5619,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>130042986</v>
+        <v>130042924</v>
       </c>
       <c r="B46" t="n">
-        <v>91605</v>
+        <v>83064</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5642,21 +5642,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1202</v>
+        <v>1467</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5666,10 +5666,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>442272</v>
+        <v>442311</v>
       </c>
       <c r="R46" t="n">
-        <v>7005763</v>
+        <v>7005788</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5701,7 +5701,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5711,12 +5711,12 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>på granlåga</t>
+          <t>På bark vid basen av gammal levande grov gran, även nordlig nållav och rostfläck och Chaenothecopsis vainioana på avverkningsstubbe under granen</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5731,12 +5731,12 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Ulrika Nordin, Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
@@ -5746,7 +5746,7 @@
         <v>130043008</v>
       </c>
       <c r="B47" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5857,56 +5857,52 @@
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Ulrika Nordin, Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>130042938</v>
+        <v>130042941</v>
       </c>
       <c r="B48" t="n">
-        <v>58375</v>
+        <v>79088</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>102125</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tallbit</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Pinicola enucleator</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Skog mellan Stenmyren och Frossjöbodarna, väster om Ågårdarna, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>442182</v>
+        <v>442223</v>
       </c>
       <c r="R48" t="n">
-        <v>7005519</v>
+        <v>7005661</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5938,7 +5934,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5948,7 +5944,12 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Rikligt på gammal gran, 40 cm långa bålar</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5975,45 +5976,49 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>130042941</v>
+        <v>130042938</v>
       </c>
       <c r="B49" t="n">
-        <v>79087</v>
+        <v>58375</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>102125</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallbit</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pinicola enucleator</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Skog mellan Stenmyren och Frossjöbodarna, väster om Ågårdarna, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>442223</v>
+        <v>442182</v>
       </c>
       <c r="R49" t="n">
-        <v>7005661</v>
+        <v>7005519</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6045,7 +6050,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6055,12 +6060,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>14:30</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Rikligt på gammal gran, 40 cm långa bålar</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6087,10 +6087,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>130042939</v>
+        <v>130042997</v>
       </c>
       <c r="B50" t="n">
-        <v>79087</v>
+        <v>57740</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6098,34 +6098,39 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Skog mellan Stenmyren och Frossjöbodarna, väster om Ågårdarna, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>442182</v>
+        <v>442161</v>
       </c>
       <c r="R50" t="n">
-        <v>7005519</v>
+        <v>7005609</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6157,7 +6162,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6167,12 +6172,12 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>Rikligt med ringhack på gran, färska och äldre</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6187,22 +6192,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Ulrika Nordin, Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>130042991</v>
+        <v>130042994</v>
       </c>
       <c r="B51" t="n">
-        <v>91605</v>
+        <v>57740</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6210,34 +6215,39 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Skog mellan Stenmyren och Frossjöbodarna, väster om Ågårdarna, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>442868</v>
+        <v>442197</v>
       </c>
       <c r="R51" t="n">
-        <v>7006112</v>
+        <v>7005760</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6269,7 +6279,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6279,12 +6289,12 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>På granlåga</t>
+          <t>Äldre Ringhack på gran</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6304,17 +6314,17 @@
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Ulrika Nordin, Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>130042997</v>
+        <v>130042991</v>
       </c>
       <c r="B52" t="n">
-        <v>57740</v>
+        <v>91606</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6322,39 +6332,34 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Skog mellan Stenmyren och Frossjöbodarna, väster om Ågårdarna, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>442161</v>
+        <v>442868</v>
       </c>
       <c r="R52" t="n">
-        <v>7005609</v>
+        <v>7006112</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6386,7 +6391,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6396,12 +6401,12 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>Rikligt med ringhack på gran, färska och äldre</t>
+          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6421,17 +6426,17 @@
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Ulrika Nordin, Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>130042994</v>
+        <v>130042983</v>
       </c>
       <c r="B53" t="n">
-        <v>57740</v>
+        <v>83059</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6439,39 +6444,34 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Skog mellan Stenmyren och Frossjöbodarna, väster om Ågårdarna, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>442197</v>
+        <v>442821</v>
       </c>
       <c r="R53" t="n">
-        <v>7005760</v>
+        <v>7006068</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6503,7 +6503,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6513,12 +6513,12 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>Äldre Ringhack på gran</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6545,10 +6545,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>130042983</v>
+        <v>130042939</v>
       </c>
       <c r="B54" t="n">
-        <v>83058</v>
+        <v>79088</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6556,21 +6556,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6580,10 +6580,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>442821</v>
+        <v>442182</v>
       </c>
       <c r="R54" t="n">
-        <v>7006068</v>
+        <v>7005519</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6615,7 +6615,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6625,7 +6625,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AC54" t="inlineStr">
@@ -6645,12 +6645,12 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
@@ -6660,7 +6660,7 @@
         <v>130042944</v>
       </c>
       <c r="B55" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6772,7 +6772,7 @@
         <v>130042943</v>
       </c>
       <c r="B56" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6881,32 +6881,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>130042933</v>
+        <v>130042989</v>
       </c>
       <c r="B57" t="n">
-        <v>83041</v>
+        <v>91606</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6439</v>
+        <v>1202</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6916,10 +6916,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>442666</v>
+        <v>442869</v>
       </c>
       <c r="R57" t="n">
-        <v>7005892</v>
+        <v>7006064</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6951,7 +6951,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6961,12 +6961,12 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>På ved på grov gammal glasbjörk i gammal granskog</t>
+          <t>på granlåga</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6981,22 +6981,22 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Ulrika Nordin, Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>130042931</v>
+        <v>130043002</v>
       </c>
       <c r="B58" t="n">
-        <v>79087</v>
+        <v>91904</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7004,21 +7004,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -7028,10 +7028,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>442535</v>
+        <v>442273</v>
       </c>
       <c r="R58" t="n">
-        <v>7005862</v>
+        <v>7005747</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7063,7 +7063,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7073,12 +7073,12 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>På gamla granar i gammal granskog</t>
+          <t>på granlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7093,22 +7093,22 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Ulrika Nordin, Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>130042926</v>
+        <v>130042936</v>
       </c>
       <c r="B59" t="n">
-        <v>80193</v>
+        <v>91602</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7116,21 +7116,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>2081</v>
+        <v>1108</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7140,10 +7140,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>442557</v>
+        <v>442119</v>
       </c>
       <c r="R59" t="n">
-        <v>7005942</v>
+        <v>7005573</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7175,7 +7175,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7185,12 +7185,12 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>Rikligt på gammal lutande sälg i kanten av gammal granskog</t>
+          <t>På död gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7217,10 +7217,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>130043002</v>
+        <v>130042926</v>
       </c>
       <c r="B60" t="n">
-        <v>91903</v>
+        <v>80194</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7228,21 +7228,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>658</v>
+        <v>2081</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7252,10 +7252,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>442273</v>
+        <v>442557</v>
       </c>
       <c r="R60" t="n">
-        <v>7005747</v>
+        <v>7005942</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7287,7 +7287,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>på granlåga i gammal granskog</t>
+          <t>Rikligt på gammal lutande sälg i kanten av gammal granskog</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7317,44 +7317,44 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Ulrika Nordin, Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>130042989</v>
+        <v>130042933</v>
       </c>
       <c r="B61" t="n">
-        <v>91605</v>
+        <v>83042</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>1202</v>
+        <v>6439</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7364,10 +7364,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>442869</v>
+        <v>442666</v>
       </c>
       <c r="R61" t="n">
-        <v>7006064</v>
+        <v>7005892</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7399,7 +7399,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7409,12 +7409,12 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>på granlåga</t>
+          <t>På ved på grov gammal glasbjörk i gammal granskog</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7429,12 +7429,12 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Ulrika Nordin, Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
@@ -7444,7 +7444,7 @@
         <v>130042945</v>
       </c>
       <c r="B62" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7553,10 +7553,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>130042936</v>
+        <v>130042931</v>
       </c>
       <c r="B63" t="n">
-        <v>91601</v>
+        <v>79088</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7564,21 +7564,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7588,10 +7588,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>442119</v>
+        <v>442535</v>
       </c>
       <c r="R63" t="n">
-        <v>7005573</v>
+        <v>7005862</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7623,7 +7623,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7633,12 +7633,12 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>På död gran i gammal granskog</t>
+          <t>På gamla granar i gammal granskog</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7658,7 +7658,7 @@
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Ulrika Nordin, Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>

--- a/artfynd/A 56618-2025 artfynd.xlsx
+++ b/artfynd/A 56618-2025 artfynd.xlsx
@@ -1917,10 +1917,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130042985</v>
+        <v>130042946</v>
       </c>
       <c r="B13" t="n">
-        <v>91606</v>
+        <v>79088</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1928,21 +1928,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1952,10 +1952,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>442272</v>
+        <v>442870</v>
       </c>
       <c r="R13" t="n">
-        <v>7005748</v>
+        <v>7006117</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1987,7 +1987,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1997,12 +1997,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>på granlåga</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2017,22 +2017,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130042946</v>
+        <v>130042980</v>
       </c>
       <c r="B14" t="n">
-        <v>79088</v>
+        <v>83059</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2040,21 +2040,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2064,10 +2064,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>442870</v>
+        <v>442510</v>
       </c>
       <c r="R14" t="n">
-        <v>7006117</v>
+        <v>7005835</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2099,7 +2099,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2109,7 +2109,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
@@ -2129,22 +2129,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130042980</v>
+        <v>130042985</v>
       </c>
       <c r="B15" t="n">
-        <v>83059</v>
+        <v>91606</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2152,21 +2152,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6440</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2176,10 +2176,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>442510</v>
+        <v>442272</v>
       </c>
       <c r="R15" t="n">
-        <v>7005835</v>
+        <v>7005748</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2211,7 +2211,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2221,12 +2221,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>på granlåga</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2365,10 +2365,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130042932</v>
+        <v>130042996</v>
       </c>
       <c r="B17" t="n">
-        <v>91602</v>
+        <v>57740</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2376,34 +2376,39 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Skog mellan Stenmyren och Frossjöbodarna, väster om Ågårdarna, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>442535</v>
+        <v>442156</v>
       </c>
       <c r="R17" t="n">
-        <v>7005862</v>
+        <v>7005705</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2435,7 +2440,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2445,12 +2450,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>På granhögstubbe i gammal granskog</t>
+          <t>Färska och äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2465,22 +2470,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Ulrika Nordin, Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Ulrika Nordin, Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130042952</v>
+        <v>130042932</v>
       </c>
       <c r="B18" t="n">
-        <v>83059</v>
+        <v>91602</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2488,21 +2493,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6440</v>
+        <v>1108</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2512,10 +2517,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>442818</v>
+        <v>442535</v>
       </c>
       <c r="R18" t="n">
-        <v>7006070</v>
+        <v>7005862</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2547,7 +2552,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2557,12 +2562,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>På gammal gran ca 25 cm i diameter</t>
+          <t>På granhögstubbe i gammal granskog</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2577,7 +2582,7 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
@@ -2589,10 +2594,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130042996</v>
+        <v>130042952</v>
       </c>
       <c r="B19" t="n">
-        <v>57740</v>
+        <v>83059</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2600,39 +2605,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Skog mellan Stenmyren och Frossjöbodarna, väster om Ågårdarna, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>442156</v>
+        <v>442818</v>
       </c>
       <c r="R19" t="n">
-        <v>7005705</v>
+        <v>7006070</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2664,7 +2664,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2674,12 +2674,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Färska och äldre ringhack på gran</t>
+          <t>På gammal gran ca 25 cm i diameter</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2694,12 +2694,12 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Ulrika Nordin, Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ulrika Nordin, Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
@@ -4169,10 +4169,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>130043007</v>
+        <v>130042993</v>
       </c>
       <c r="B33" t="n">
-        <v>79088</v>
+        <v>57740</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4180,34 +4180,39 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Skog mellan Stenmyren och Frossjöbodarna, väster om Ågårdarna, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>442871</v>
+        <v>442270</v>
       </c>
       <c r="R33" t="n">
-        <v>7006059</v>
+        <v>7005830</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4239,7 +4244,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4249,12 +4254,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>På gamla granar i gammal granskog</t>
+          <t>Äldre Ringhack på gran</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4281,45 +4286,49 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130042937</v>
+        <v>130042925</v>
       </c>
       <c r="B34" t="n">
-        <v>79088</v>
+        <v>57844</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>103031</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Skog mellan Stenmyren och Frossjöbodarna, väster om Ågårdarna, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>442119</v>
+        <v>442557</v>
       </c>
       <c r="R34" t="n">
-        <v>7005573</v>
+        <v>7005942</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4351,7 +4360,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4361,12 +4370,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>I gammal granskog</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4386,17 +4395,17 @@
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Ulrika Nordin, Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130042993</v>
+        <v>130043007</v>
       </c>
       <c r="B35" t="n">
-        <v>57740</v>
+        <v>79088</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4404,39 +4413,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Skog mellan Stenmyren och Frossjöbodarna, väster om Ågårdarna, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>442270</v>
+        <v>442871</v>
       </c>
       <c r="R35" t="n">
-        <v>7005830</v>
+        <v>7006059</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4468,7 +4472,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4478,12 +4482,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Äldre Ringhack på gran</t>
+          <t>På gamla granar i gammal granskog</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4510,49 +4514,45 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>130042925</v>
+        <v>130042937</v>
       </c>
       <c r="B36" t="n">
-        <v>57844</v>
+        <v>79088</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>103031</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Skog mellan Stenmyren och Frossjöbodarna, väster om Ågårdarna, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>442557</v>
+        <v>442119</v>
       </c>
       <c r="R36" t="n">
-        <v>7005942</v>
+        <v>7005573</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4584,7 +4584,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4594,12 +4594,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>I gammal granskog</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4619,7 +4619,7 @@
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Ulrika Nordin, Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
@@ -4738,10 +4738,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>130043001</v>
+        <v>130042995</v>
       </c>
       <c r="B38" t="n">
-        <v>83064</v>
+        <v>57740</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4749,34 +4749,39 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1467</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Skog mellan Stenmyren och Frossjöbodarna, väster om Ågårdarna, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>442691</v>
+        <v>442161</v>
       </c>
       <c r="R38" t="n">
-        <v>7005901</v>
+        <v>7005744</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4808,7 +4813,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4818,12 +4823,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4850,10 +4855,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>130042961</v>
+        <v>130043001</v>
       </c>
       <c r="B39" t="n">
-        <v>91626</v>
+        <v>83064</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4861,19 +4866,23 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5432</v>
+        <v>1467</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr"/>
+          <t>Sclerophora coniophaea</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+        </is>
+      </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -4881,10 +4890,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>442177</v>
+        <v>442691</v>
       </c>
       <c r="R39" t="n">
-        <v>7005633</v>
+        <v>7005901</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4916,7 +4925,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4926,12 +4935,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>På död gran ca 37 cm i diameter</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4946,19 +4955,19 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Ulrika Nordin, Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Ulrika Nordin, Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>130042935</v>
+        <v>130042961</v>
       </c>
       <c r="B40" t="n">
         <v>91626</v>
@@ -4989,10 +4998,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>442524</v>
+        <v>442177</v>
       </c>
       <c r="R40" t="n">
-        <v>7005879</v>
+        <v>7005633</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5024,7 +5033,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5034,12 +5043,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>På död gran i gammal granskog</t>
+          <t>På död gran ca 37 cm i diameter</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5054,22 +5063,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Ulrika Nordin, Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>130042995</v>
+        <v>130042935</v>
       </c>
       <c r="B41" t="n">
-        <v>57740</v>
+        <v>91626</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5077,39 +5086,30 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Skog mellan Stenmyren och Frossjöbodarna, väster om Ågårdarna, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>442161</v>
+        <v>442524</v>
       </c>
       <c r="R41" t="n">
-        <v>7005744</v>
+        <v>7005879</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5141,7 +5141,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>På död gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5171,12 +5171,12 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Ulrika Nordin, Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
@@ -6087,10 +6087,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>130042997</v>
+        <v>130042991</v>
       </c>
       <c r="B50" t="n">
-        <v>57740</v>
+        <v>91606</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6098,39 +6098,34 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Skog mellan Stenmyren och Frossjöbodarna, väster om Ågårdarna, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>442161</v>
+        <v>442868</v>
       </c>
       <c r="R50" t="n">
-        <v>7005609</v>
+        <v>7006112</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6162,7 +6157,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6172,12 +6167,12 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Rikligt med ringhack på gran, färska och äldre</t>
+          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6204,10 +6199,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>130042994</v>
+        <v>130042983</v>
       </c>
       <c r="B51" t="n">
-        <v>57740</v>
+        <v>83059</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6215,39 +6210,34 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Skog mellan Stenmyren och Frossjöbodarna, väster om Ågårdarna, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>442197</v>
+        <v>442821</v>
       </c>
       <c r="R51" t="n">
-        <v>7005760</v>
+        <v>7006068</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6279,7 +6269,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6289,12 +6279,12 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Äldre Ringhack på gran</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6314,17 +6304,17 @@
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Ulrika Nordin, Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>130042991</v>
+        <v>130042939</v>
       </c>
       <c r="B52" t="n">
-        <v>91606</v>
+        <v>79088</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6332,21 +6322,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6356,10 +6346,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>442868</v>
+        <v>442182</v>
       </c>
       <c r="R52" t="n">
-        <v>7006112</v>
+        <v>7005519</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6391,7 +6381,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6401,12 +6391,12 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>På granlåga</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6421,22 +6411,22 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Ulrika Nordin, Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>130042983</v>
+        <v>130042994</v>
       </c>
       <c r="B53" t="n">
-        <v>83059</v>
+        <v>57740</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6444,34 +6434,39 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Skog mellan Stenmyren och Frossjöbodarna, väster om Ågårdarna, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>442821</v>
+        <v>442197</v>
       </c>
       <c r="R53" t="n">
-        <v>7006068</v>
+        <v>7005760</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6503,7 +6498,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6513,12 +6508,12 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>Äldre Ringhack på gran</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6538,17 +6533,17 @@
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Ulrika Nordin, Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>130042939</v>
+        <v>130042997</v>
       </c>
       <c r="B54" t="n">
-        <v>79088</v>
+        <v>57740</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6556,34 +6551,39 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Skog mellan Stenmyren och Frossjöbodarna, väster om Ågårdarna, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>442182</v>
+        <v>442161</v>
       </c>
       <c r="R54" t="n">
-        <v>7005519</v>
+        <v>7005609</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6615,7 +6615,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6625,12 +6625,12 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>Rikligt med ringhack på gran, färska och äldre</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6645,12 +6645,12 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Ulrika Nordin, Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
@@ -6881,10 +6881,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>130042989</v>
+        <v>130042926</v>
       </c>
       <c r="B57" t="n">
-        <v>91606</v>
+        <v>80194</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6892,21 +6892,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1202</v>
+        <v>2081</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6916,10 +6916,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>442869</v>
+        <v>442557</v>
       </c>
       <c r="R57" t="n">
-        <v>7006064</v>
+        <v>7005942</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6951,7 +6951,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6961,12 +6961,12 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>på granlåga</t>
+          <t>Rikligt på gammal lutande sälg i kanten av gammal granskog</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6981,44 +6981,44 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Ulrika Nordin, Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ulrika Nordin, Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>130043002</v>
+        <v>130042933</v>
       </c>
       <c r="B58" t="n">
-        <v>91904</v>
+        <v>83042</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>658</v>
+        <v>6439</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -7028,10 +7028,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>442273</v>
+        <v>442666</v>
       </c>
       <c r="R58" t="n">
-        <v>7005747</v>
+        <v>7005892</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7063,7 +7063,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7073,12 +7073,12 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>på granlåga i gammal granskog</t>
+          <t>På ved på grov gammal glasbjörk i gammal granskog</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7093,22 +7093,22 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Ulrika Nordin, Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ulrika Nordin, Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>130042936</v>
+        <v>130042945</v>
       </c>
       <c r="B59" t="n">
-        <v>91602</v>
+        <v>79088</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7116,21 +7116,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7140,10 +7140,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>442119</v>
+        <v>442853</v>
       </c>
       <c r="R59" t="n">
-        <v>7005573</v>
+        <v>7006058</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7175,7 +7175,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7185,12 +7185,12 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>På död gran i gammal granskog</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7217,10 +7217,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>130042926</v>
+        <v>130042931</v>
       </c>
       <c r="B60" t="n">
-        <v>80194</v>
+        <v>79088</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7228,21 +7228,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7252,10 +7252,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>442557</v>
+        <v>442535</v>
       </c>
       <c r="R60" t="n">
-        <v>7005942</v>
+        <v>7005862</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7287,7 +7287,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>Rikligt på gammal lutande sälg i kanten av gammal granskog</t>
+          <t>På gamla granar i gammal granskog</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7329,32 +7329,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>130042933</v>
+        <v>130042989</v>
       </c>
       <c r="B61" t="n">
-        <v>83042</v>
+        <v>91606</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6439</v>
+        <v>1202</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7364,10 +7364,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>442666</v>
+        <v>442869</v>
       </c>
       <c r="R61" t="n">
-        <v>7005892</v>
+        <v>7006064</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7399,7 +7399,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7409,12 +7409,12 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>På ved på grov gammal glasbjörk i gammal granskog</t>
+          <t>på granlåga</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7429,22 +7429,22 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Ulrika Nordin, Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Ulrika Nordin, Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>130042945</v>
+        <v>130043002</v>
       </c>
       <c r="B62" t="n">
-        <v>79088</v>
+        <v>91904</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7452,21 +7452,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7476,10 +7476,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>442853</v>
+        <v>442273</v>
       </c>
       <c r="R62" t="n">
-        <v>7006058</v>
+        <v>7005747</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7511,7 +7511,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7521,12 +7521,12 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>på granlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7541,22 +7541,22 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Ulrika Nordin, Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>130042931</v>
+        <v>130042936</v>
       </c>
       <c r="B63" t="n">
-        <v>79088</v>
+        <v>91602</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7564,21 +7564,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7588,10 +7588,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>442535</v>
+        <v>442119</v>
       </c>
       <c r="R63" t="n">
-        <v>7005862</v>
+        <v>7005573</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7623,7 +7623,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7633,12 +7633,12 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>På gamla granar i gammal granskog</t>
+          <t>På död gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7658,7 +7658,7 @@
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Ulrika Nordin, Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>

--- a/artfynd/A 56618-2025 artfynd.xlsx
+++ b/artfynd/A 56618-2025 artfynd.xlsx
@@ -1917,10 +1917,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130042946</v>
+        <v>130042985</v>
       </c>
       <c r="B13" t="n">
-        <v>79088</v>
+        <v>91606</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1928,21 +1928,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1952,10 +1952,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>442870</v>
+        <v>442272</v>
       </c>
       <c r="R13" t="n">
-        <v>7006117</v>
+        <v>7005748</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1987,7 +1987,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1997,12 +1997,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>på granlåga</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2017,22 +2017,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130042980</v>
+        <v>130042946</v>
       </c>
       <c r="B14" t="n">
-        <v>83059</v>
+        <v>79088</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2040,21 +2040,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2064,10 +2064,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>442510</v>
+        <v>442870</v>
       </c>
       <c r="R14" t="n">
-        <v>7005835</v>
+        <v>7006117</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2099,7 +2099,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2109,7 +2109,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
@@ -2129,22 +2129,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130042985</v>
+        <v>130042980</v>
       </c>
       <c r="B15" t="n">
-        <v>91606</v>
+        <v>83059</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2152,21 +2152,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>6440</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2176,10 +2176,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>442272</v>
+        <v>442510</v>
       </c>
       <c r="R15" t="n">
-        <v>7005748</v>
+        <v>7005835</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2211,7 +2211,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2221,12 +2221,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>på granlåga</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2365,10 +2365,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130042996</v>
+        <v>130042932</v>
       </c>
       <c r="B17" t="n">
-        <v>57740</v>
+        <v>91602</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2376,39 +2376,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Skog mellan Stenmyren och Frossjöbodarna, väster om Ågårdarna, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>442156</v>
+        <v>442535</v>
       </c>
       <c r="R17" t="n">
-        <v>7005705</v>
+        <v>7005862</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2440,7 +2435,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2450,12 +2445,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Färska och äldre ringhack på gran</t>
+          <t>På granhögstubbe i gammal granskog</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2470,22 +2465,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Ulrika Nordin, Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ulrika Nordin, Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130042932</v>
+        <v>130042952</v>
       </c>
       <c r="B18" t="n">
-        <v>91602</v>
+        <v>83059</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2493,21 +2488,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1108</v>
+        <v>6440</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2517,10 +2512,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>442535</v>
+        <v>442818</v>
       </c>
       <c r="R18" t="n">
-        <v>7005862</v>
+        <v>7006070</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2552,7 +2547,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2562,12 +2557,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>På granhögstubbe i gammal granskog</t>
+          <t>På gammal gran ca 25 cm i diameter</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2582,7 +2577,7 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
@@ -2594,10 +2589,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130042952</v>
+        <v>130042996</v>
       </c>
       <c r="B19" t="n">
-        <v>83059</v>
+        <v>57740</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2605,34 +2600,39 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Skog mellan Stenmyren och Frossjöbodarna, väster om Ågårdarna, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>442818</v>
+        <v>442156</v>
       </c>
       <c r="R19" t="n">
-        <v>7006070</v>
+        <v>7005705</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2664,7 +2664,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2674,12 +2674,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>På gammal gran ca 25 cm i diameter</t>
+          <t>Färska och äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2694,22 +2694,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Ulrika Nordin, Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Ulrika Nordin, Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130042916</v>
+        <v>130042960</v>
       </c>
       <c r="B20" t="n">
-        <v>91606</v>
+        <v>78100</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2717,21 +2717,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>228579</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2741,10 +2741,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>442264</v>
+        <v>442328</v>
       </c>
       <c r="R20" t="n">
-        <v>7005760</v>
+        <v>7005788</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2776,7 +2776,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2786,12 +2786,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>På granlåga</t>
+          <t>På gammal gran ca 30 cm i diameter</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2806,7 +2806,7 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
@@ -2818,10 +2818,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130042960</v>
+        <v>130042916</v>
       </c>
       <c r="B21" t="n">
-        <v>78100</v>
+        <v>91606</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2829,21 +2829,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>228579</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2853,10 +2853,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>442328</v>
+        <v>442264</v>
       </c>
       <c r="R21" t="n">
-        <v>7005788</v>
+        <v>7005760</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2888,7 +2888,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2898,12 +2898,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>På gammal gran ca 30 cm i diameter</t>
+          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2918,7 +2918,7 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
@@ -2930,32 +2930,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130042956</v>
+        <v>130042988</v>
       </c>
       <c r="B22" t="n">
-        <v>83057</v>
+        <v>91606</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6486</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Skuggnål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Chaenotheca sphaerocephala</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2965,10 +2965,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>442534</v>
+        <v>442709</v>
       </c>
       <c r="R22" t="n">
-        <v>7005878</v>
+        <v>7006059</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3000,7 +3000,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3010,12 +3010,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Vid basen av gran ca 40 cm i diameter</t>
+          <t>på granlåga</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3030,19 +3030,19 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Ulrika Nordin, Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Ulrika Nordin, Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130042988</v>
+        <v>130042987</v>
       </c>
       <c r="B23" t="n">
         <v>91606</v>
@@ -3077,10 +3077,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>442709</v>
+        <v>442685</v>
       </c>
       <c r="R23" t="n">
-        <v>7006059</v>
+        <v>7005938</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3122,7 +3122,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
@@ -3154,10 +3154,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130042987</v>
+        <v>130042934</v>
       </c>
       <c r="B24" t="n">
-        <v>91606</v>
+        <v>91626</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3165,23 +3165,19 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3189,10 +3185,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>442685</v>
+        <v>442211</v>
       </c>
       <c r="R24" t="n">
-        <v>7005938</v>
+        <v>7005732</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3224,7 +3220,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3234,12 +3230,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>på granlåga</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3254,22 +3250,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Ulrika Nordin, Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ulrika Nordin, Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130042981</v>
+        <v>130042954</v>
       </c>
       <c r="B25" t="n">
-        <v>83059</v>
+        <v>57740</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3277,34 +3273,39 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Skog mellan Stenmyren och Frossjöbodarna, väster om Ågårdarna, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>442640</v>
+        <v>442278</v>
       </c>
       <c r="R25" t="n">
-        <v>7005904</v>
+        <v>7005808</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3336,7 +3337,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3346,12 +3347,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>Rikligt med färska ringhack på gran ca 40 cm i diameter</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3366,42 +3367,46 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Ulrika Nordin, Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130042934</v>
+        <v>130042929</v>
       </c>
       <c r="B26" t="n">
-        <v>91626</v>
+        <v>97669</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5432</v>
+        <v>221945</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr"/>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3409,10 +3414,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>442211</v>
+        <v>442265</v>
       </c>
       <c r="R26" t="n">
-        <v>7005732</v>
+        <v>7005695</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3444,7 +3449,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3454,12 +3459,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>På marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3486,10 +3491,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130042954</v>
+        <v>130042981</v>
       </c>
       <c r="B27" t="n">
-        <v>57740</v>
+        <v>83059</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3497,39 +3502,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Skog mellan Stenmyren och Frossjöbodarna, väster om Ågårdarna, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>442278</v>
+        <v>442640</v>
       </c>
       <c r="R27" t="n">
-        <v>7005808</v>
+        <v>7005904</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3561,7 +3561,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3571,12 +3571,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Rikligt med färska ringhack på gran ca 40 cm i diameter</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3591,44 +3591,44 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Ulrika Nordin, Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130042929</v>
+        <v>130042956</v>
       </c>
       <c r="B28" t="n">
-        <v>97669</v>
+        <v>83057</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>221945</v>
+        <v>6486</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Skuggnål</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Chaenotheca sphaerocephala</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3638,10 +3638,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>442265</v>
+        <v>442534</v>
       </c>
       <c r="R28" t="n">
-        <v>7005695</v>
+        <v>7005878</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3673,7 +3673,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3683,12 +3683,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>På marken i gammal granskog</t>
+          <t>Vid basen av gran ca 40 cm i diameter</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3703,7 +3703,7 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
@@ -3715,32 +3715,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130043005</v>
+        <v>130042922</v>
       </c>
       <c r="B29" t="n">
-        <v>91602</v>
+        <v>75071</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1108</v>
+        <v>6428</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3750,10 +3750,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>442514</v>
+        <v>442311</v>
       </c>
       <c r="R29" t="n">
-        <v>7005889</v>
+        <v>7005788</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3785,7 +3785,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3795,12 +3795,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>På granhögstubbe</t>
+          <t>På ved på gammal avverkningsstubbe under grov gammal gran</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3815,12 +3815,12 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Ulrika Nordin, Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ulrika Nordin, Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
@@ -3940,32 +3940,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130042922</v>
+        <v>130043005</v>
       </c>
       <c r="B31" t="n">
-        <v>75071</v>
+        <v>91602</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6428</v>
+        <v>1108</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3975,10 +3975,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>442311</v>
+        <v>442514</v>
       </c>
       <c r="R31" t="n">
-        <v>7005788</v>
+        <v>7005889</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4010,7 +4010,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4020,12 +4020,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>På ved på gammal avverkningsstubbe under grov gammal gran</t>
+          <t>På granhögstubbe</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4040,12 +4040,12 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Ulrika Nordin, Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Ulrika Nordin, Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
@@ -6087,10 +6087,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>130042991</v>
+        <v>130042997</v>
       </c>
       <c r="B50" t="n">
-        <v>91606</v>
+        <v>57740</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6098,34 +6098,39 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Skog mellan Stenmyren och Frossjöbodarna, väster om Ågårdarna, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>442868</v>
+        <v>442161</v>
       </c>
       <c r="R50" t="n">
-        <v>7006112</v>
+        <v>7005609</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6157,7 +6162,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6167,12 +6172,12 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>På granlåga</t>
+          <t>Rikligt med ringhack på gran, färska och äldre</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6199,10 +6204,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>130042983</v>
+        <v>130042994</v>
       </c>
       <c r="B51" t="n">
-        <v>83059</v>
+        <v>57740</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6210,34 +6215,39 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Skog mellan Stenmyren och Frossjöbodarna, väster om Ågårdarna, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>442821</v>
+        <v>442197</v>
       </c>
       <c r="R51" t="n">
-        <v>7006068</v>
+        <v>7005760</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6269,7 +6279,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6279,12 +6289,12 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>Äldre Ringhack på gran</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6304,17 +6314,17 @@
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Ulrika Nordin, Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>130042939</v>
+        <v>130042991</v>
       </c>
       <c r="B52" t="n">
-        <v>79088</v>
+        <v>91606</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6322,21 +6332,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6346,10 +6356,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>442182</v>
+        <v>442868</v>
       </c>
       <c r="R52" t="n">
-        <v>7005519</v>
+        <v>7006112</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6381,7 +6391,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6391,12 +6401,12 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6411,22 +6421,22 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Ulrika Nordin, Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>130042994</v>
+        <v>130042983</v>
       </c>
       <c r="B53" t="n">
-        <v>57740</v>
+        <v>83059</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6434,39 +6444,34 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Skog mellan Stenmyren och Frossjöbodarna, väster om Ågårdarna, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>442197</v>
+        <v>442821</v>
       </c>
       <c r="R53" t="n">
-        <v>7005760</v>
+        <v>7006068</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6498,7 +6503,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6508,12 +6513,12 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>Äldre Ringhack på gran</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6533,17 +6538,17 @@
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Ulrika Nordin, Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>130042997</v>
+        <v>130042939</v>
       </c>
       <c r="B54" t="n">
-        <v>57740</v>
+        <v>79088</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6551,39 +6556,34 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Skog mellan Stenmyren och Frossjöbodarna, väster om Ågårdarna, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>442161</v>
+        <v>442182</v>
       </c>
       <c r="R54" t="n">
-        <v>7005609</v>
+        <v>7005519</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6615,7 +6615,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6625,12 +6625,12 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>Rikligt med ringhack på gran, färska och äldre</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6645,12 +6645,12 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Ulrika Nordin, Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
@@ -6881,10 +6881,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>130042926</v>
+        <v>130042989</v>
       </c>
       <c r="B57" t="n">
-        <v>80194</v>
+        <v>91606</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6892,21 +6892,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>2081</v>
+        <v>1202</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6916,10 +6916,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>442557</v>
+        <v>442869</v>
       </c>
       <c r="R57" t="n">
-        <v>7005942</v>
+        <v>7006064</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6951,7 +6951,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6961,12 +6961,12 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>Rikligt på gammal lutande sälg i kanten av gammal granskog</t>
+          <t>på granlåga</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6981,44 +6981,44 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Ulrika Nordin, Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Ulrika Nordin, Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>130042933</v>
+        <v>130043002</v>
       </c>
       <c r="B58" t="n">
-        <v>83042</v>
+        <v>91904</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6439</v>
+        <v>658</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -7028,10 +7028,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>442666</v>
+        <v>442273</v>
       </c>
       <c r="R58" t="n">
-        <v>7005892</v>
+        <v>7005747</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7063,7 +7063,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7073,12 +7073,12 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>På ved på grov gammal glasbjörk i gammal granskog</t>
+          <t>på granlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7093,22 +7093,22 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Ulrika Nordin, Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Ulrika Nordin, Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>130042945</v>
+        <v>130042936</v>
       </c>
       <c r="B59" t="n">
-        <v>79088</v>
+        <v>91602</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7116,21 +7116,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7140,10 +7140,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>442853</v>
+        <v>442119</v>
       </c>
       <c r="R59" t="n">
-        <v>7006058</v>
+        <v>7005573</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7175,7 +7175,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7185,12 +7185,12 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>På död gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7217,10 +7217,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>130042931</v>
+        <v>130042926</v>
       </c>
       <c r="B60" t="n">
-        <v>79088</v>
+        <v>80194</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7228,21 +7228,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7252,10 +7252,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>442535</v>
+        <v>442557</v>
       </c>
       <c r="R60" t="n">
-        <v>7005862</v>
+        <v>7005942</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7287,7 +7287,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>På gamla granar i gammal granskog</t>
+          <t>Rikligt på gammal lutande sälg i kanten av gammal granskog</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7329,32 +7329,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>130042989</v>
+        <v>130042933</v>
       </c>
       <c r="B61" t="n">
-        <v>91606</v>
+        <v>83042</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>1202</v>
+        <v>6439</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7364,10 +7364,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>442869</v>
+        <v>442666</v>
       </c>
       <c r="R61" t="n">
-        <v>7006064</v>
+        <v>7005892</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7399,7 +7399,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7409,12 +7409,12 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>på granlåga</t>
+          <t>På ved på grov gammal glasbjörk i gammal granskog</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7429,22 +7429,22 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Ulrika Nordin, Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ulrika Nordin, Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>130043002</v>
+        <v>130042945</v>
       </c>
       <c r="B62" t="n">
-        <v>91904</v>
+        <v>79088</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7452,21 +7452,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7476,10 +7476,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>442273</v>
+        <v>442853</v>
       </c>
       <c r="R62" t="n">
-        <v>7005747</v>
+        <v>7006058</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7511,7 +7511,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7521,12 +7521,12 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>på granlåga i gammal granskog</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7541,22 +7541,22 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Ulrika Nordin, Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>130042936</v>
+        <v>130042931</v>
       </c>
       <c r="B63" t="n">
-        <v>91602</v>
+        <v>79088</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7564,21 +7564,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7588,10 +7588,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>442119</v>
+        <v>442535</v>
       </c>
       <c r="R63" t="n">
-        <v>7005573</v>
+        <v>7005862</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7623,7 +7623,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7633,12 +7633,12 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>På död gran i gammal granskog</t>
+          <t>På gamla granar i gammal granskog</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7658,7 +7658,7 @@
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Ulrika Nordin, Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>

--- a/artfynd/A 56618-2025 artfynd.xlsx
+++ b/artfynd/A 56618-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130042984</v>
+        <v>130042928</v>
       </c>
       <c r="B2" t="n">
-        <v>91606</v>
+        <v>78504</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>502</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Ladlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Calicium tigillare</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Pers.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>442318</v>
+        <v>442500</v>
       </c>
       <c r="R2" t="n">
-        <v>7005873</v>
+        <v>7005787</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,12 +755,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>På gammal granlåga</t>
+          <t>På ved på gammal barrhögstubbe i gammal granskog</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,22 +775,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130042928</v>
+        <v>130042984</v>
       </c>
       <c r="B3" t="n">
-        <v>78503</v>
+        <v>91623</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -798,21 +798,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>502</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ladlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Calicium tigillare</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Pers.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>442500</v>
+        <v>442318</v>
       </c>
       <c r="R3" t="n">
-        <v>7005787</v>
+        <v>7005873</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,7 +857,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -867,12 +867,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>På ved på gammal barrhögstubbe i gammal granskog</t>
+          <t>På gammal granlåga</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,12 +887,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Ulrika Nordin, Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -902,7 +902,7 @@
         <v>130043006</v>
       </c>
       <c r="B4" t="n">
-        <v>91602</v>
+        <v>91619</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1004,17 +1004,17 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Ulrika Nordin, Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130042951</v>
+        <v>130042999</v>
       </c>
       <c r="B5" t="n">
-        <v>78100</v>
+        <v>57740</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1022,34 +1022,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>228579</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Skog mellan Stenmyren och Frossjöbodarna, väster om Ågårdarna, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>442818</v>
+        <v>442253</v>
       </c>
       <c r="R5" t="n">
-        <v>7006070</v>
+        <v>7005683</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1081,7 +1086,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1091,12 +1096,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>På gammal gran ca 25 cm i diameter</t>
+          <t>Ringhack på två närliggande granar, ett färskt, ett äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1111,12 +1116,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Ulrika Nordin, Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1233,17 +1238,17 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Ulrika Nordin, Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130042999</v>
+        <v>130042951</v>
       </c>
       <c r="B7" t="n">
-        <v>57740</v>
+        <v>78101</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1251,39 +1256,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>228579</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Skog mellan Stenmyren och Frossjöbodarna, väster om Ågårdarna, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>442253</v>
+        <v>442818</v>
       </c>
       <c r="R7" t="n">
-        <v>7005683</v>
+        <v>7006070</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1315,7 +1315,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1325,12 +1325,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ringhack på två närliggande granar, ett färskt, ett äldre</t>
+          <t>På gammal gran ca 25 cm i diameter</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1345,22 +1345,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Ulrika Nordin, Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ulrika Nordin, Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130043004</v>
+        <v>130042955</v>
       </c>
       <c r="B8" t="n">
-        <v>91602</v>
+        <v>79089</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1368,21 +1368,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1392,10 +1392,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>442160</v>
+        <v>442534</v>
       </c>
       <c r="R8" t="n">
-        <v>7005610</v>
+        <v>7005878</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1427,7 +1427,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1437,12 +1437,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>På gran</t>
+          <t>På gran, 40 cm diameter</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1457,22 +1457,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Ulrika Nordin, Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ulrika Nordin, Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130043003</v>
+        <v>130043004</v>
       </c>
       <c r="B9" t="n">
-        <v>78100</v>
+        <v>91619</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1480,21 +1480,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>228579</v>
+        <v>1108</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1504,10 +1504,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>442219</v>
+        <v>442160</v>
       </c>
       <c r="R9" t="n">
-        <v>7005641</v>
+        <v>7005610</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1539,7 +1539,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1549,12 +1549,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>på gammal gran i gammal granskog</t>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1574,17 +1574,17 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Ulrika Nordin, Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130042955</v>
+        <v>130043003</v>
       </c>
       <c r="B10" t="n">
-        <v>79088</v>
+        <v>78101</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1592,21 +1592,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1616,10 +1616,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>442534</v>
+        <v>442219</v>
       </c>
       <c r="R10" t="n">
-        <v>7005878</v>
+        <v>7005641</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1651,7 +1651,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1661,12 +1661,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>På gran, 40 cm diameter</t>
+          <t>på gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1681,44 +1681,44 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Ulrika Nordin, Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130042992</v>
+        <v>130042927</v>
       </c>
       <c r="B11" t="n">
-        <v>92324</v>
+        <v>80194</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>3298</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1728,10 +1728,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>442209</v>
+        <v>442557</v>
       </c>
       <c r="R11" t="n">
-        <v>7005642</v>
+        <v>7005942</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1763,7 +1763,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1773,12 +1773,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>På gran</t>
+          <t>Rikligt på gammal lutande sälg, Rikligt med apothecier</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1793,44 +1793,44 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Ulrika Nordin, Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130042927</v>
+        <v>130042992</v>
       </c>
       <c r="B12" t="n">
-        <v>80193</v>
+        <v>92341</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>3298</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1840,10 +1840,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>442557</v>
+        <v>442209</v>
       </c>
       <c r="R12" t="n">
-        <v>7005942</v>
+        <v>7005642</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1875,7 +1875,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1885,12 +1885,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Rikligt på gammal lutande sälg, Rikligt med apothecier</t>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1905,22 +1905,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Ulrika Nordin, Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130042985</v>
+        <v>130042946</v>
       </c>
       <c r="B13" t="n">
-        <v>91606</v>
+        <v>79089</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1928,21 +1928,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1952,10 +1952,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>442272</v>
+        <v>442870</v>
       </c>
       <c r="R13" t="n">
-        <v>7005748</v>
+        <v>7006117</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1987,7 +1987,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1997,12 +1997,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>på granlåga</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2017,22 +2017,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130042946</v>
+        <v>130042985</v>
       </c>
       <c r="B14" t="n">
-        <v>79088</v>
+        <v>91623</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2040,21 +2040,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2064,10 +2064,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>442870</v>
+        <v>442272</v>
       </c>
       <c r="R14" t="n">
-        <v>7006117</v>
+        <v>7005748</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2099,7 +2099,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2109,12 +2109,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>på granlåga</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2129,12 +2129,12 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -2144,7 +2144,7 @@
         <v>130042980</v>
       </c>
       <c r="B15" t="n">
-        <v>83059</v>
+        <v>83065</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2256,7 +2256,7 @@
         <v>130042923</v>
       </c>
       <c r="B16" t="n">
-        <v>83054</v>
+        <v>83060</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2358,17 +2358,17 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Ulrika Nordin, Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130042932</v>
+        <v>130042996</v>
       </c>
       <c r="B17" t="n">
-        <v>91602</v>
+        <v>57740</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2376,34 +2376,39 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Skog mellan Stenmyren och Frossjöbodarna, väster om Ågårdarna, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>442535</v>
+        <v>442156</v>
       </c>
       <c r="R17" t="n">
-        <v>7005862</v>
+        <v>7005705</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2435,7 +2440,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2445,12 +2450,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>På granhögstubbe i gammal granskog</t>
+          <t>Färska och äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2465,22 +2470,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Ulrika Nordin, Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130042952</v>
+        <v>130042932</v>
       </c>
       <c r="B18" t="n">
-        <v>83059</v>
+        <v>91619</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2488,21 +2493,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6440</v>
+        <v>1108</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2512,10 +2517,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>442818</v>
+        <v>442535</v>
       </c>
       <c r="R18" t="n">
-        <v>7006070</v>
+        <v>7005862</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2547,7 +2552,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2557,12 +2562,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>På gammal gran ca 25 cm i diameter</t>
+          <t>På granhögstubbe i gammal granskog</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2577,22 +2582,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Ulrika Nordin, Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130042996</v>
+        <v>130042952</v>
       </c>
       <c r="B19" t="n">
-        <v>57740</v>
+        <v>83065</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2600,39 +2605,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Skog mellan Stenmyren och Frossjöbodarna, väster om Ågårdarna, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>442156</v>
+        <v>442818</v>
       </c>
       <c r="R19" t="n">
-        <v>7005705</v>
+        <v>7006070</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2664,7 +2664,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2674,12 +2674,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Färska och äldre ringhack på gran</t>
+          <t>På gammal gran ca 25 cm i diameter</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2694,22 +2694,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Ulrika Nordin, Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ulrika Nordin, Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130042960</v>
+        <v>130042916</v>
       </c>
       <c r="B20" t="n">
-        <v>78100</v>
+        <v>91623</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2717,21 +2717,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>228579</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2741,10 +2741,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>442328</v>
+        <v>442264</v>
       </c>
       <c r="R20" t="n">
-        <v>7005788</v>
+        <v>7005760</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2776,7 +2776,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2786,12 +2786,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>På gammal gran ca 30 cm i diameter</t>
+          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2806,22 +2806,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Ulrika Nordin, Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130042916</v>
+        <v>130042960</v>
       </c>
       <c r="B21" t="n">
-        <v>91606</v>
+        <v>78101</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2829,21 +2829,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>228579</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2853,10 +2853,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>442264</v>
+        <v>442328</v>
       </c>
       <c r="R21" t="n">
-        <v>7005760</v>
+        <v>7005788</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2888,7 +2888,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2898,12 +2898,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>På granlåga</t>
+          <t>På gammal gran ca 30 cm i diameter</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2918,7 +2918,7 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
@@ -2933,7 +2933,7 @@
         <v>130042988</v>
       </c>
       <c r="B22" t="n">
-        <v>91606</v>
+        <v>91623</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3035,7 +3035,7 @@
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Ulrika Nordin, Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
@@ -3045,7 +3045,7 @@
         <v>130042987</v>
       </c>
       <c r="B23" t="n">
-        <v>91606</v>
+        <v>91623</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3147,7 +3147,7 @@
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Ulrika Nordin, Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
@@ -3157,7 +3157,7 @@
         <v>130042934</v>
       </c>
       <c r="B24" t="n">
-        <v>91626</v>
+        <v>91643</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3255,57 +3255,52 @@
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Ulrika Nordin, Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130042954</v>
+        <v>130042956</v>
       </c>
       <c r="B25" t="n">
-        <v>57740</v>
+        <v>83063</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>6486</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skuggnål</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca sphaerocephala</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Skog mellan Stenmyren och Frossjöbodarna, väster om Ågårdarna, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>442278</v>
+        <v>442534</v>
       </c>
       <c r="R25" t="n">
-        <v>7005808</v>
+        <v>7005878</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3337,7 +3332,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3347,12 +3342,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Rikligt med färska ringhack på gran ca 40 cm i diameter</t>
+          <t>Vid basen av gran ca 40 cm i diameter</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3379,32 +3374,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130042929</v>
+        <v>130042981</v>
       </c>
       <c r="B26" t="n">
-        <v>97669</v>
+        <v>83065</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>221945</v>
+        <v>6440</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3414,10 +3409,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>442265</v>
+        <v>442640</v>
       </c>
       <c r="R26" t="n">
-        <v>7005695</v>
+        <v>7005904</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3449,7 +3444,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3459,12 +3454,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>På marken i gammal granskog</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3479,22 +3474,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Ulrika Nordin, Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130042981</v>
+        <v>130042954</v>
       </c>
       <c r="B27" t="n">
-        <v>83059</v>
+        <v>57740</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3502,34 +3497,39 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Skog mellan Stenmyren och Frossjöbodarna, väster om Ågårdarna, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>442640</v>
+        <v>442278</v>
       </c>
       <c r="R27" t="n">
-        <v>7005904</v>
+        <v>7005808</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3561,7 +3561,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3571,12 +3571,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>Rikligt med färska ringhack på gran ca 40 cm i diameter</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3591,44 +3591,44 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Ulrika Nordin, Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130042956</v>
+        <v>130042929</v>
       </c>
       <c r="B28" t="n">
-        <v>83057</v>
+        <v>97686</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6486</v>
+        <v>221945</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Skuggnål</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Chaenotheca sphaerocephala</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3638,10 +3638,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>442534</v>
+        <v>442265</v>
       </c>
       <c r="R28" t="n">
-        <v>7005878</v>
+        <v>7005695</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3673,7 +3673,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3683,12 +3683,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Vid basen av gran ca 40 cm i diameter</t>
+          <t>På marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3703,44 +3703,44 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Ulrika Nordin, Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130042922</v>
+        <v>130043005</v>
       </c>
       <c r="B29" t="n">
-        <v>75071</v>
+        <v>91619</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6428</v>
+        <v>1108</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3750,10 +3750,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>442311</v>
+        <v>442514</v>
       </c>
       <c r="R29" t="n">
-        <v>7005788</v>
+        <v>7005889</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3785,7 +3785,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3795,12 +3795,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>På ved på gammal avverkningsstubbe under grov gammal gran</t>
+          <t>På granhögstubbe</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3815,44 +3815,44 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Ulrika Nordin, Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130042953</v>
+        <v>130042922</v>
       </c>
       <c r="B30" t="n">
-        <v>78111</v>
+        <v>75072</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>314</v>
+        <v>6428</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vitskaftad svartspik</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Chaenothecopsis viridialba</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Kremp.) A.F.W.Schmidt</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3862,10 +3862,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>442818</v>
+        <v>442311</v>
       </c>
       <c r="R30" t="n">
-        <v>7006070</v>
+        <v>7005788</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3897,7 +3897,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>På gammal gran ca 25 cm i diameter</t>
+          <t>På ved på gammal avverkningsstubbe under grov gammal gran</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3921,29 +3921,28 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Ulrika Nordin, Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130043005</v>
+        <v>130042953</v>
       </c>
       <c r="B31" t="n">
-        <v>91602</v>
+        <v>78112</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3951,21 +3950,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1108</v>
+        <v>314</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Vitskaftad svartspik</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Chaenothecopsis viridialba</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Kremp.) A.F.W.Schmidt</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3975,10 +3974,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>442514</v>
+        <v>442818</v>
       </c>
       <c r="R31" t="n">
-        <v>7005889</v>
+        <v>7006070</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4010,7 +4009,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4020,12 +4019,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>På granhögstubbe</t>
+          <t>På gammal gran ca 25 cm i diameter</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4034,18 +4033,19 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Ulrika Nordin, Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ulrika Nordin, Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
@@ -4162,17 +4162,17 @@
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Ulrika Nordin, Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>130042993</v>
+        <v>130042937</v>
       </c>
       <c r="B33" t="n">
-        <v>57740</v>
+        <v>79089</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4180,39 +4180,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Skog mellan Stenmyren och Frossjöbodarna, väster om Ågårdarna, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>442270</v>
+        <v>442119</v>
       </c>
       <c r="R33" t="n">
-        <v>7005830</v>
+        <v>7005573</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4244,7 +4239,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4254,12 +4249,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Äldre Ringhack på gran</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4274,61 +4269,57 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Ulrika Nordin, Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130042925</v>
+        <v>130043007</v>
       </c>
       <c r="B34" t="n">
-        <v>57844</v>
+        <v>79089</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>103031</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Skog mellan Stenmyren och Frossjöbodarna, väster om Ågårdarna, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>442557</v>
+        <v>442871</v>
       </c>
       <c r="R34" t="n">
-        <v>7005942</v>
+        <v>7006059</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4360,7 +4351,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4370,12 +4361,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>I gammal granskog</t>
+          <t>På gamla granar i gammal granskog</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4390,22 +4381,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Ulrika Nordin, Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130043007</v>
+        <v>130042993</v>
       </c>
       <c r="B35" t="n">
-        <v>79088</v>
+        <v>57740</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4413,34 +4404,39 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Skog mellan Stenmyren och Frossjöbodarna, väster om Ågårdarna, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>442871</v>
+        <v>442270</v>
       </c>
       <c r="R35" t="n">
-        <v>7006059</v>
+        <v>7005830</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4472,7 +4468,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4482,12 +4478,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>På gamla granar i gammal granskog</t>
+          <t>Äldre Ringhack på gran</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4507,52 +4503,56 @@
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Ulrika Nordin, Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>130042937</v>
+        <v>130042925</v>
       </c>
       <c r="B36" t="n">
-        <v>79088</v>
+        <v>57844</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>103031</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Skog mellan Stenmyren och Frossjöbodarna, väster om Ågårdarna, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>442119</v>
+        <v>442557</v>
       </c>
       <c r="R36" t="n">
-        <v>7005573</v>
+        <v>7005942</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4584,7 +4584,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4594,12 +4594,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>I gammal granskog</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4629,7 +4629,7 @@
         <v>130042942</v>
       </c>
       <c r="B37" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4738,10 +4738,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>130042995</v>
+        <v>130043001</v>
       </c>
       <c r="B38" t="n">
-        <v>57740</v>
+        <v>83070</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4749,39 +4749,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>1467</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Skog mellan Stenmyren och Frossjöbodarna, väster om Ågårdarna, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>442161</v>
+        <v>442691</v>
       </c>
       <c r="R38" t="n">
-        <v>7005744</v>
+        <v>7005901</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4813,7 +4808,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4823,12 +4818,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4848,17 +4843,17 @@
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Ulrika Nordin, Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>130043001</v>
+        <v>130042935</v>
       </c>
       <c r="B39" t="n">
-        <v>83064</v>
+        <v>91643</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4866,23 +4861,19 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1467</v>
+        <v>5432</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr"/>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -4890,10 +4881,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>442691</v>
+        <v>442524</v>
       </c>
       <c r="R39" t="n">
-        <v>7005901</v>
+        <v>7005879</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4925,7 +4916,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4935,12 +4926,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>På död gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4955,12 +4946,12 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Ulrika Nordin, Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
@@ -4970,7 +4961,7 @@
         <v>130042961</v>
       </c>
       <c r="B40" t="n">
-        <v>91626</v>
+        <v>91643</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5075,10 +5066,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>130042935</v>
+        <v>130042995</v>
       </c>
       <c r="B41" t="n">
-        <v>91626</v>
+        <v>57740</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5086,30 +5077,39 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Skog mellan Stenmyren och Frossjöbodarna, väster om Ågårdarna, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>442524</v>
+        <v>442161</v>
       </c>
       <c r="R41" t="n">
-        <v>7005879</v>
+        <v>7005744</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5141,7 +5141,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>På död gran i gammal granskog</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5171,44 +5171,44 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>130042982</v>
+        <v>130042940</v>
       </c>
       <c r="B42" t="n">
-        <v>83059</v>
+        <v>98719</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6440</v>
+        <v>220093</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5218,10 +5218,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>442693</v>
+        <v>442223</v>
       </c>
       <c r="R42" t="n">
-        <v>7005900</v>
+        <v>7005661</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5253,7 +5253,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5263,12 +5263,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>På marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5283,22 +5283,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>130042959</v>
+        <v>130042982</v>
       </c>
       <c r="B43" t="n">
-        <v>83059</v>
+        <v>83065</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5330,10 +5330,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>442328</v>
+        <v>442693</v>
       </c>
       <c r="R43" t="n">
-        <v>7005788</v>
+        <v>7005900</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5365,7 +5365,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5375,12 +5375,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>På gammal gran ca 30 cm i diameter</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5395,44 +5395,44 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Ulrika Nordin, Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>130042940</v>
+        <v>130042959</v>
       </c>
       <c r="B44" t="n">
-        <v>98702</v>
+        <v>83065</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220093</v>
+        <v>6440</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5442,10 +5442,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>442223</v>
+        <v>442328</v>
       </c>
       <c r="R44" t="n">
-        <v>7005661</v>
+        <v>7005788</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5477,7 +5477,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5487,12 +5487,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>På marken i gammal granskog</t>
+          <t>På gammal gran ca 30 cm i diameter</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5507,12 +5507,12 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Ulrika Nordin, Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
@@ -5522,7 +5522,7 @@
         <v>130042986</v>
       </c>
       <c r="B45" t="n">
-        <v>91606</v>
+        <v>91623</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5634,7 +5634,7 @@
         <v>130042924</v>
       </c>
       <c r="B46" t="n">
-        <v>83064</v>
+        <v>83070</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5736,17 +5736,17 @@
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Ulrika Nordin, Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>130043008</v>
+        <v>130042941</v>
       </c>
       <c r="B47" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5771,26 +5771,17 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+      <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Skog mellan Stenmyren och Frossjöbodarna, väster om Ågårdarna, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>442754</v>
+        <v>442223</v>
       </c>
       <c r="R47" t="n">
-        <v>7006003</v>
+        <v>7005661</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5822,7 +5813,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5832,12 +5823,12 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>20 bålar på gammal gran</t>
+          <t>Rikligt på gammal gran, 40 cm långa bålar</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5852,22 +5843,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Ulrika Nordin, Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>130042941</v>
+        <v>130043008</v>
       </c>
       <c r="B48" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5892,17 +5883,26 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I48" t="inlineStr"/>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Skog mellan Stenmyren och Frossjöbodarna, väster om Ågårdarna, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>442223</v>
+        <v>442754</v>
       </c>
       <c r="R48" t="n">
-        <v>7005661</v>
+        <v>7006003</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5934,7 +5934,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5944,12 +5944,12 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Rikligt på gammal gran, 40 cm långa bålar</t>
+          <t>20 bålar på gammal gran</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5964,12 +5964,12 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
@@ -5979,7 +5979,7 @@
         <v>130042938</v>
       </c>
       <c r="B49" t="n">
-        <v>58375</v>
+        <v>58376</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6087,10 +6087,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>130042997</v>
+        <v>130042983</v>
       </c>
       <c r="B50" t="n">
-        <v>57740</v>
+        <v>83065</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6098,39 +6098,34 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Skog mellan Stenmyren och Frossjöbodarna, väster om Ågårdarna, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>442161</v>
+        <v>442821</v>
       </c>
       <c r="R50" t="n">
-        <v>7005609</v>
+        <v>7006068</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6162,7 +6157,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6172,12 +6167,12 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Rikligt med ringhack på gran, färska och äldre</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6197,7 +6192,7 @@
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Ulrika Nordin, Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
@@ -6314,17 +6309,17 @@
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Ulrika Nordin, Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>130042991</v>
+        <v>130042997</v>
       </c>
       <c r="B52" t="n">
-        <v>91606</v>
+        <v>57740</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6332,34 +6327,39 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Skog mellan Stenmyren och Frossjöbodarna, väster om Ågårdarna, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>442868</v>
+        <v>442161</v>
       </c>
       <c r="R52" t="n">
-        <v>7006112</v>
+        <v>7005609</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6391,7 +6391,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6401,12 +6401,12 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>På granlåga</t>
+          <t>Rikligt med ringhack på gran, färska och äldre</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6426,17 +6426,17 @@
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Ulrika Nordin, Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>130042983</v>
+        <v>130042991</v>
       </c>
       <c r="B53" t="n">
-        <v>83059</v>
+        <v>91623</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6444,21 +6444,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6440</v>
+        <v>1202</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6468,10 +6468,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>442821</v>
+        <v>442868</v>
       </c>
       <c r="R53" t="n">
-        <v>7006068</v>
+        <v>7006112</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6503,7 +6503,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6513,12 +6513,12 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6548,7 +6548,7 @@
         <v>130042939</v>
       </c>
       <c r="B54" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6660,7 +6660,7 @@
         <v>130042944</v>
       </c>
       <c r="B55" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6772,7 +6772,7 @@
         <v>130042943</v>
       </c>
       <c r="B56" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6881,32 +6881,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>130042989</v>
+        <v>130042933</v>
       </c>
       <c r="B57" t="n">
-        <v>91606</v>
+        <v>83048</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1202</v>
+        <v>6439</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6916,10 +6916,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>442869</v>
+        <v>442666</v>
       </c>
       <c r="R57" t="n">
-        <v>7006064</v>
+        <v>7005892</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6951,7 +6951,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6961,12 +6961,12 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>på granlåga</t>
+          <t>På ved på grov gammal glasbjörk i gammal granskog</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6981,22 +6981,22 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Ulrika Nordin, Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>130043002</v>
+        <v>130042931</v>
       </c>
       <c r="B58" t="n">
-        <v>91904</v>
+        <v>79089</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7004,21 +7004,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -7028,10 +7028,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>442273</v>
+        <v>442535</v>
       </c>
       <c r="R58" t="n">
-        <v>7005747</v>
+        <v>7005862</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7063,7 +7063,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7073,12 +7073,12 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>på granlåga i gammal granskog</t>
+          <t>På gamla granar i gammal granskog</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7093,22 +7093,22 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Ulrika Nordin, Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>130042936</v>
+        <v>130042945</v>
       </c>
       <c r="B59" t="n">
-        <v>91602</v>
+        <v>79089</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7116,21 +7116,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7140,10 +7140,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>442119</v>
+        <v>442853</v>
       </c>
       <c r="R59" t="n">
-        <v>7005573</v>
+        <v>7006058</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7175,7 +7175,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7185,12 +7185,12 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>På död gran i gammal granskog</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7217,10 +7217,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>130042926</v>
+        <v>130043002</v>
       </c>
       <c r="B60" t="n">
-        <v>80194</v>
+        <v>91921</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7228,21 +7228,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>2081</v>
+        <v>658</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7252,10 +7252,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>442557</v>
+        <v>442273</v>
       </c>
       <c r="R60" t="n">
-        <v>7005942</v>
+        <v>7005747</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7287,7 +7287,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>Rikligt på gammal lutande sälg i kanten av gammal granskog</t>
+          <t>på granlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7317,44 +7317,44 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Ulrika Nordin, Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>130042933</v>
+        <v>130042989</v>
       </c>
       <c r="B61" t="n">
-        <v>83042</v>
+        <v>91623</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6439</v>
+        <v>1202</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7364,10 +7364,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>442666</v>
+        <v>442869</v>
       </c>
       <c r="R61" t="n">
-        <v>7005892</v>
+        <v>7006064</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7399,7 +7399,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7409,12 +7409,12 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>På ved på grov gammal glasbjörk i gammal granskog</t>
+          <t>på granlåga</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7429,22 +7429,22 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Ulrika Nordin, Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>130042945</v>
+        <v>130042936</v>
       </c>
       <c r="B62" t="n">
-        <v>79088</v>
+        <v>91619</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7452,21 +7452,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7476,10 +7476,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>442853</v>
+        <v>442119</v>
       </c>
       <c r="R62" t="n">
-        <v>7006058</v>
+        <v>7005573</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7511,7 +7511,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7521,12 +7521,12 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>På död gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7553,10 +7553,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>130042931</v>
+        <v>130042926</v>
       </c>
       <c r="B63" t="n">
-        <v>79088</v>
+        <v>80195</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7564,21 +7564,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7588,10 +7588,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>442535</v>
+        <v>442557</v>
       </c>
       <c r="R63" t="n">
-        <v>7005862</v>
+        <v>7005942</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7623,7 +7623,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7633,12 +7633,12 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>På gamla granar i gammal granskog</t>
+          <t>Rikligt på gammal lutande sälg i kanten av gammal granskog</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7658,7 +7658,7 @@
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Ulrika Nordin, Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>

--- a/artfynd/A 56618-2025 artfynd.xlsx
+++ b/artfynd/A 56618-2025 artfynd.xlsx
@@ -1357,10 +1357,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130042955</v>
+        <v>130043003</v>
       </c>
       <c r="B8" t="n">
-        <v>79095</v>
+        <v>78107</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1368,21 +1368,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1392,10 +1392,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>442534</v>
+        <v>442219</v>
       </c>
       <c r="R8" t="n">
-        <v>7005878</v>
+        <v>7005641</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1427,7 +1427,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1437,12 +1437,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>På gran, 40 cm diameter</t>
+          <t>på gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1457,22 +1457,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Ulrika Nordin, Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130043004</v>
+        <v>130042955</v>
       </c>
       <c r="B9" t="n">
-        <v>91635</v>
+        <v>79095</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1480,21 +1480,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1504,10 +1504,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>442160</v>
+        <v>442534</v>
       </c>
       <c r="R9" t="n">
-        <v>7005610</v>
+        <v>7005878</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1539,7 +1539,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1549,12 +1549,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>På gran</t>
+          <t>På gran, 40 cm diameter</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1569,22 +1569,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Ulrika Nordin, Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130043003</v>
+        <v>130043004</v>
       </c>
       <c r="B10" t="n">
-        <v>78107</v>
+        <v>91635</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1592,21 +1592,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>228579</v>
+        <v>1108</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1616,10 +1616,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>442219</v>
+        <v>442160</v>
       </c>
       <c r="R10" t="n">
-        <v>7005641</v>
+        <v>7005610</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1651,7 +1651,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1661,12 +1661,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>på gammal gran i gammal granskog</t>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -2365,10 +2365,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130042932</v>
+        <v>130042952</v>
       </c>
       <c r="B17" t="n">
-        <v>91635</v>
+        <v>83073</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2376,21 +2376,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1108</v>
+        <v>6440</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2400,10 +2400,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>442535</v>
+        <v>442818</v>
       </c>
       <c r="R17" t="n">
-        <v>7005862</v>
+        <v>7006070</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2435,7 +2435,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2445,12 +2445,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>På granhögstubbe i gammal granskog</t>
+          <t>På gammal gran ca 25 cm i diameter</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2465,22 +2465,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Ulrika Nordin, Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130042952</v>
+        <v>130042932</v>
       </c>
       <c r="B18" t="n">
-        <v>83073</v>
+        <v>91635</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2488,21 +2488,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6440</v>
+        <v>1108</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2512,10 +2512,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>442818</v>
+        <v>442535</v>
       </c>
       <c r="R18" t="n">
-        <v>7006070</v>
+        <v>7005862</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2547,7 +2547,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2557,12 +2557,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>På gammal gran ca 25 cm i diameter</t>
+          <t>På granhögstubbe i gammal granskog</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2577,12 +2577,12 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Ulrika Nordin, Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -3715,32 +3715,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130043005</v>
+        <v>130042922</v>
       </c>
       <c r="B29" t="n">
-        <v>91635</v>
+        <v>75073</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1108</v>
+        <v>6428</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3750,10 +3750,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>442514</v>
+        <v>442311</v>
       </c>
       <c r="R29" t="n">
-        <v>7005889</v>
+        <v>7005788</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3785,7 +3785,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3795,12 +3795,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>På granhögstubbe</t>
+          <t>På ved på gammal avverkningsstubbe under grov gammal gran</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3815,22 +3815,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130042917</v>
+        <v>130043005</v>
       </c>
       <c r="B30" t="n">
-        <v>57741</v>
+        <v>91635</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3838,39 +3838,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Skog mellan Stenmyren och Frossjöbodarna, väster om Ågårdarna, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>442320</v>
+        <v>442514</v>
       </c>
       <c r="R30" t="n">
-        <v>7005822</v>
+        <v>7005889</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3902,7 +3897,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3912,12 +3907,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Rikligt med ringhack på 55 cm grov gammal gran</t>
+          <t>På granhögstubbe</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3932,44 +3927,44 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130042922</v>
+        <v>130042953</v>
       </c>
       <c r="B31" t="n">
-        <v>75073</v>
+        <v>78118</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6428</v>
+        <v>314</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Vitskaftad svartspik</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Chaenothecopsis viridialba</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Kremp.) A.F.W.Schmidt</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3979,10 +3974,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>442311</v>
+        <v>442818</v>
       </c>
       <c r="R31" t="n">
-        <v>7005788</v>
+        <v>7006070</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4014,7 +4009,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4024,12 +4019,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>På ved på gammal avverkningsstubbe under grov gammal gran</t>
+          <t>På gammal gran ca 25 cm i diameter</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4038,28 +4033,29 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Ulrika Nordin, Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130042953</v>
+        <v>130042917</v>
       </c>
       <c r="B32" t="n">
-        <v>78118</v>
+        <v>57741</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4067,34 +4063,39 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>314</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vitskaftad svartspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Chaenothecopsis viridialba</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Kremp.) A.F.W.Schmidt</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Skog mellan Stenmyren och Frossjöbodarna, väster om Ågårdarna, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>442818</v>
+        <v>442320</v>
       </c>
       <c r="R32" t="n">
-        <v>7006070</v>
+        <v>7005822</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4126,7 +4127,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4136,12 +4137,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>På gammal gran ca 25 cm i diameter</t>
+          <t>Rikligt med ringhack på 55 cm grov gammal gran</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4150,19 +4151,18 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Ulrika Nordin, Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
@@ -6881,32 +6881,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>130042933</v>
+        <v>130042926</v>
       </c>
       <c r="B57" t="n">
-        <v>83056</v>
+        <v>80201</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6439</v>
+        <v>2081</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6916,10 +6916,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>442666</v>
+        <v>442557</v>
       </c>
       <c r="R57" t="n">
-        <v>7005892</v>
+        <v>7005942</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6951,7 +6951,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6961,12 +6961,12 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>På ved på grov gammal glasbjörk i gammal granskog</t>
+          <t>Rikligt på gammal lutande sälg i kanten av gammal granskog</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6993,10 +6993,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>130042945</v>
+        <v>130042936</v>
       </c>
       <c r="B58" t="n">
-        <v>79095</v>
+        <v>91635</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7004,21 +7004,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -7028,10 +7028,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>442853</v>
+        <v>442119</v>
       </c>
       <c r="R58" t="n">
-        <v>7006058</v>
+        <v>7005573</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7063,7 +7063,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7073,12 +7073,12 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>På död gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7105,32 +7105,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>130042931</v>
+        <v>130042933</v>
       </c>
       <c r="B59" t="n">
-        <v>79095</v>
+        <v>83056</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>6439</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7140,10 +7140,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>442535</v>
+        <v>442666</v>
       </c>
       <c r="R59" t="n">
-        <v>7005862</v>
+        <v>7005892</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7175,7 +7175,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7185,12 +7185,12 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>På gamla granar i gammal granskog</t>
+          <t>På ved på grov gammal glasbjörk i gammal granskog</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7217,10 +7217,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>130042989</v>
+        <v>130042945</v>
       </c>
       <c r="B60" t="n">
-        <v>91639</v>
+        <v>79095</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7228,21 +7228,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7252,10 +7252,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>442869</v>
+        <v>442853</v>
       </c>
       <c r="R60" t="n">
-        <v>7006064</v>
+        <v>7006058</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7287,7 +7287,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>på granlåga</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7317,22 +7317,22 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>130042926</v>
+        <v>130042931</v>
       </c>
       <c r="B61" t="n">
-        <v>80201</v>
+        <v>79095</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7340,21 +7340,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7364,10 +7364,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>442557</v>
+        <v>442535</v>
       </c>
       <c r="R61" t="n">
-        <v>7005942</v>
+        <v>7005862</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7399,7 +7399,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7409,12 +7409,12 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>Rikligt på gammal lutande sälg i kanten av gammal granskog</t>
+          <t>På gamla granar i gammal granskog</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7441,10 +7441,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>130043002</v>
+        <v>130042989</v>
       </c>
       <c r="B62" t="n">
-        <v>91937</v>
+        <v>91639</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7452,21 +7452,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7476,10 +7476,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>442273</v>
+        <v>442869</v>
       </c>
       <c r="R62" t="n">
-        <v>7005747</v>
+        <v>7006064</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7511,7 +7511,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7521,12 +7521,12 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>på granlåga i gammal granskog</t>
+          <t>på granlåga</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7553,10 +7553,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>130042936</v>
+        <v>130043002</v>
       </c>
       <c r="B63" t="n">
-        <v>91635</v>
+        <v>91937</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7564,21 +7564,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>1108</v>
+        <v>658</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7588,10 +7588,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>442119</v>
+        <v>442273</v>
       </c>
       <c r="R63" t="n">
-        <v>7005573</v>
+        <v>7005747</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7623,7 +7623,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7633,12 +7633,12 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>På död gran i gammal granskog</t>
+          <t>på granlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7653,12 +7653,12 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>

--- a/artfynd/A 56618-2025 artfynd.xlsx
+++ b/artfynd/A 56618-2025 artfynd.xlsx
@@ -1469,10 +1469,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130042955</v>
+        <v>130043004</v>
       </c>
       <c r="B9" t="n">
-        <v>79095</v>
+        <v>91635</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1480,21 +1480,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1504,10 +1504,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>442534</v>
+        <v>442160</v>
       </c>
       <c r="R9" t="n">
-        <v>7005878</v>
+        <v>7005610</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1539,7 +1539,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1549,12 +1549,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>På gran, 40 cm diameter</t>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1569,22 +1569,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Ulrika Nordin, Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130043004</v>
+        <v>130042955</v>
       </c>
       <c r="B10" t="n">
-        <v>91635</v>
+        <v>79095</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1592,21 +1592,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1616,10 +1616,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>442160</v>
+        <v>442534</v>
       </c>
       <c r="R10" t="n">
-        <v>7005610</v>
+        <v>7005878</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1651,7 +1651,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1661,12 +1661,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>På gran</t>
+          <t>På gran, 40 cm diameter</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1681,12 +1681,12 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Ulrika Nordin, Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
@@ -2365,10 +2365,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130042952</v>
+        <v>130042932</v>
       </c>
       <c r="B17" t="n">
-        <v>83073</v>
+        <v>91635</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2376,21 +2376,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6440</v>
+        <v>1108</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2400,10 +2400,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>442818</v>
+        <v>442535</v>
       </c>
       <c r="R17" t="n">
-        <v>7006070</v>
+        <v>7005862</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2435,7 +2435,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2445,12 +2445,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>På gammal gran ca 25 cm i diameter</t>
+          <t>På granhögstubbe i gammal granskog</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2465,22 +2465,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Ulrika Nordin, Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130042932</v>
+        <v>130042952</v>
       </c>
       <c r="B18" t="n">
-        <v>91635</v>
+        <v>83073</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2488,21 +2488,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1108</v>
+        <v>6440</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2512,10 +2512,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>442535</v>
+        <v>442818</v>
       </c>
       <c r="R18" t="n">
-        <v>7005862</v>
+        <v>7006070</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2547,7 +2547,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2557,12 +2557,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>På granhögstubbe i gammal granskog</t>
+          <t>På gammal gran ca 25 cm i diameter</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2577,12 +2577,12 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Ulrika Nordin, Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -2930,10 +2930,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130042934</v>
+        <v>130042981</v>
       </c>
       <c r="B22" t="n">
-        <v>91659</v>
+        <v>83073</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2941,19 +2941,23 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5432</v>
+        <v>6440</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr"/>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2961,10 +2965,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>442211</v>
+        <v>442640</v>
       </c>
       <c r="R22" t="n">
-        <v>7005732</v>
+        <v>7005904</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2996,7 +3000,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3006,12 +3010,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3026,62 +3030,57 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130042954</v>
+        <v>130042956</v>
       </c>
       <c r="B23" t="n">
-        <v>57741</v>
+        <v>83071</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>6486</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skuggnål</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca sphaerocephala</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Skog mellan Stenmyren och Frossjöbodarna, väster om Ågårdarna, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>442278</v>
+        <v>442534</v>
       </c>
       <c r="R23" t="n">
-        <v>7005808</v>
+        <v>7005878</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3113,7 +3112,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3123,12 +3122,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Rikligt med färska ringhack på gran ca 40 cm i diameter</t>
+          <t>Vid basen av gran ca 40 cm i diameter</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3155,34 +3154,30 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130042929</v>
+        <v>130042934</v>
       </c>
       <c r="B24" t="n">
-        <v>97702</v>
+        <v>91659</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>221945</v>
+        <v>5432</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3190,10 +3185,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>442265</v>
+        <v>442211</v>
       </c>
       <c r="R24" t="n">
-        <v>7005695</v>
+        <v>7005732</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3225,7 +3220,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3235,12 +3230,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>På marken i gammal granskog</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3267,45 +3262,50 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130042956</v>
+        <v>130042954</v>
       </c>
       <c r="B25" t="n">
-        <v>83071</v>
+        <v>57741</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6486</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Skuggnål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Chaenotheca sphaerocephala</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Skog mellan Stenmyren och Frossjöbodarna, väster om Ågårdarna, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>442534</v>
+        <v>442278</v>
       </c>
       <c r="R25" t="n">
-        <v>7005878</v>
+        <v>7005808</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3337,7 +3337,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3347,12 +3347,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Vid basen av gran ca 40 cm i diameter</t>
+          <t>Rikligt med färska ringhack på gran ca 40 cm i diameter</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3491,10 +3491,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130042981</v>
+        <v>130042987</v>
       </c>
       <c r="B27" t="n">
-        <v>83073</v>
+        <v>91639</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3502,21 +3502,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6440</v>
+        <v>1202</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3526,10 +3526,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>442640</v>
+        <v>442685</v>
       </c>
       <c r="R27" t="n">
-        <v>7005904</v>
+        <v>7005938</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3561,7 +3561,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3571,12 +3571,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>på granlåga</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3603,32 +3603,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130042987</v>
+        <v>130042929</v>
       </c>
       <c r="B28" t="n">
-        <v>91639</v>
+        <v>97702</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1202</v>
+        <v>221945</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3638,10 +3638,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>442685</v>
+        <v>442265</v>
       </c>
       <c r="R28" t="n">
-        <v>7005938</v>
+        <v>7005695</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3673,7 +3673,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3683,12 +3683,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>på granlåga</t>
+          <t>På marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3703,44 +3703,44 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130042922</v>
+        <v>130043005</v>
       </c>
       <c r="B29" t="n">
-        <v>75073</v>
+        <v>91635</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6428</v>
+        <v>1108</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3750,10 +3750,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>442311</v>
+        <v>442514</v>
       </c>
       <c r="R29" t="n">
-        <v>7005788</v>
+        <v>7005889</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3785,7 +3785,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3795,12 +3795,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>På ved på gammal avverkningsstubbe under grov gammal gran</t>
+          <t>På granhögstubbe</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3815,22 +3815,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130043005</v>
+        <v>130042917</v>
       </c>
       <c r="B30" t="n">
-        <v>91635</v>
+        <v>57741</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3838,34 +3838,39 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Skog mellan Stenmyren och Frossjöbodarna, väster om Ågårdarna, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>442514</v>
+        <v>442320</v>
       </c>
       <c r="R30" t="n">
-        <v>7005889</v>
+        <v>7005822</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3897,7 +3902,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3907,12 +3912,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>På granhögstubbe</t>
+          <t>Rikligt med ringhack på 55 cm grov gammal gran</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3927,44 +3932,44 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130042953</v>
+        <v>130042922</v>
       </c>
       <c r="B31" t="n">
-        <v>78118</v>
+        <v>75073</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>314</v>
+        <v>6428</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vitskaftad svartspik</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Chaenothecopsis viridialba</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Kremp.) A.F.W.Schmidt</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3974,10 +3979,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>442818</v>
+        <v>442311</v>
       </c>
       <c r="R31" t="n">
-        <v>7006070</v>
+        <v>7005788</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4009,7 +4014,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4019,12 +4024,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>På gammal gran ca 25 cm i diameter</t>
+          <t>På ved på gammal avverkningsstubbe under grov gammal gran</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4033,29 +4038,28 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Ulrika Nordin, Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130042917</v>
+        <v>130042953</v>
       </c>
       <c r="B32" t="n">
-        <v>57741</v>
+        <v>78118</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4063,39 +4067,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>314</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitskaftad svartspik</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenothecopsis viridialba</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Kremp.) A.F.W.Schmidt</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Skog mellan Stenmyren och Frossjöbodarna, väster om Ågårdarna, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>442320</v>
+        <v>442818</v>
       </c>
       <c r="R32" t="n">
-        <v>7005822</v>
+        <v>7006070</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4127,7 +4126,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4137,12 +4136,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Rikligt med ringhack på 55 cm grov gammal gran</t>
+          <t>På gammal gran ca 25 cm i diameter</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4151,18 +4150,19 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Ulrika Nordin, Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
@@ -4738,10 +4738,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>130043001</v>
+        <v>130042995</v>
       </c>
       <c r="B38" t="n">
-        <v>83078</v>
+        <v>57741</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4749,34 +4749,39 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1467</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Skog mellan Stenmyren och Frossjöbodarna, väster om Ågårdarna, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>442691</v>
+        <v>442161</v>
       </c>
       <c r="R38" t="n">
-        <v>7005901</v>
+        <v>7005744</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4808,7 +4813,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4818,12 +4823,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4850,10 +4855,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>130042961</v>
+        <v>130043001</v>
       </c>
       <c r="B39" t="n">
-        <v>91659</v>
+        <v>83078</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4861,19 +4866,23 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5432</v>
+        <v>1467</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr"/>
+          <t>Sclerophora coniophaea</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+        </is>
+      </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -4881,10 +4890,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>442177</v>
+        <v>442691</v>
       </c>
       <c r="R39" t="n">
-        <v>7005633</v>
+        <v>7005901</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4916,7 +4925,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4926,12 +4935,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>På död gran ca 37 cm i diameter</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4946,19 +4955,19 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Ulrika Nordin, Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>130042935</v>
+        <v>130042961</v>
       </c>
       <c r="B40" t="n">
         <v>91659</v>
@@ -4989,10 +4998,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>442524</v>
+        <v>442177</v>
       </c>
       <c r="R40" t="n">
-        <v>7005879</v>
+        <v>7005633</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5024,7 +5033,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5034,12 +5043,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>På död gran i gammal granskog</t>
+          <t>På död gran ca 37 cm i diameter</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5054,22 +5063,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Ulrika Nordin, Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>130042995</v>
+        <v>130042935</v>
       </c>
       <c r="B41" t="n">
-        <v>57741</v>
+        <v>91659</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5077,39 +5086,30 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Skog mellan Stenmyren och Frossjöbodarna, väster om Ågårdarna, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>442161</v>
+        <v>442524</v>
       </c>
       <c r="R41" t="n">
-        <v>7005744</v>
+        <v>7005879</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5141,7 +5141,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>På död gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5171,12 +5171,12 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
@@ -6087,10 +6087,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>130042991</v>
+        <v>130042983</v>
       </c>
       <c r="B50" t="n">
-        <v>91639</v>
+        <v>83073</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6098,21 +6098,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1202</v>
+        <v>6440</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6122,10 +6122,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>442868</v>
+        <v>442821</v>
       </c>
       <c r="R50" t="n">
-        <v>7006112</v>
+        <v>7006068</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6157,7 +6157,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6167,12 +6167,12 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>På granlåga</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6199,10 +6199,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>130042997</v>
+        <v>130042939</v>
       </c>
       <c r="B51" t="n">
-        <v>57741</v>
+        <v>79095</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6210,39 +6210,34 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Skog mellan Stenmyren och Frossjöbodarna, väster om Ågårdarna, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>442161</v>
+        <v>442182</v>
       </c>
       <c r="R51" t="n">
-        <v>7005609</v>
+        <v>7005519</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6274,7 +6269,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6284,12 +6279,12 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Rikligt med ringhack på gran, färska och äldre</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6304,22 +6299,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>130042994</v>
+        <v>130042991</v>
       </c>
       <c r="B52" t="n">
-        <v>57741</v>
+        <v>91639</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6327,39 +6322,34 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Skog mellan Stenmyren och Frossjöbodarna, väster om Ågårdarna, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>442197</v>
+        <v>442868</v>
       </c>
       <c r="R52" t="n">
-        <v>7005760</v>
+        <v>7006112</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6391,7 +6381,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6401,12 +6391,12 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>Äldre Ringhack på gran</t>
+          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6433,10 +6423,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>130042983</v>
+        <v>130042997</v>
       </c>
       <c r="B53" t="n">
-        <v>83073</v>
+        <v>57741</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6444,34 +6434,39 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Skog mellan Stenmyren och Frossjöbodarna, väster om Ågårdarna, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>442821</v>
+        <v>442161</v>
       </c>
       <c r="R53" t="n">
-        <v>7006068</v>
+        <v>7005609</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6503,7 +6498,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6513,12 +6508,12 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>Rikligt med ringhack på gran, färska och äldre</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6545,10 +6540,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>130042939</v>
+        <v>130042994</v>
       </c>
       <c r="B54" t="n">
-        <v>79095</v>
+        <v>57741</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6556,34 +6551,39 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Skog mellan Stenmyren och Frossjöbodarna, väster om Ågårdarna, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>442182</v>
+        <v>442197</v>
       </c>
       <c r="R54" t="n">
-        <v>7005519</v>
+        <v>7005760</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6615,7 +6615,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6625,12 +6625,12 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>Äldre Ringhack på gran</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6645,12 +6645,12 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>

--- a/artfynd/A 56618-2025 artfynd.xlsx
+++ b/artfynd/A 56618-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130042984</v>
+        <v>130042928</v>
       </c>
       <c r="B2" t="n">
-        <v>91639</v>
+        <v>78510</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>502</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Ladlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Calicium tigillare</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Pers.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>442318</v>
+        <v>442500</v>
       </c>
       <c r="R2" t="n">
-        <v>7005873</v>
+        <v>7005787</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,12 +755,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>På gammal granlåga</t>
+          <t>På ved på gammal barrhögstubbe i gammal granskog</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,22 +775,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130042928</v>
+        <v>130042984</v>
       </c>
       <c r="B3" t="n">
-        <v>78510</v>
+        <v>91641</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -798,21 +798,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>502</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ladlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Calicium tigillare</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Pers.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>442500</v>
+        <v>442318</v>
       </c>
       <c r="R3" t="n">
-        <v>7005787</v>
+        <v>7005873</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,7 +857,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -867,12 +867,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>På ved på gammal barrhögstubbe i gammal granskog</t>
+          <t>På gammal granlåga</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,12 +887,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -902,7 +902,7 @@
         <v>130043006</v>
       </c>
       <c r="B4" t="n">
-        <v>91635</v>
+        <v>91637</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1472,7 +1472,7 @@
         <v>130043004</v>
       </c>
       <c r="B9" t="n">
-        <v>91635</v>
+        <v>91637</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1693,32 +1693,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130042927</v>
+        <v>130042992</v>
       </c>
       <c r="B11" t="n">
-        <v>80200</v>
+        <v>92359</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>3298</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1728,10 +1728,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>442557</v>
+        <v>442209</v>
       </c>
       <c r="R11" t="n">
-        <v>7005942</v>
+        <v>7005642</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1763,7 +1763,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1773,12 +1773,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Rikligt på gammal lutande sälg, Rikligt med apothecier</t>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1793,44 +1793,44 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130042992</v>
+        <v>130042927</v>
       </c>
       <c r="B12" t="n">
-        <v>92357</v>
+        <v>80200</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>3298</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1840,10 +1840,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>442209</v>
+        <v>442557</v>
       </c>
       <c r="R12" t="n">
-        <v>7005642</v>
+        <v>7005942</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1875,7 +1875,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1885,12 +1885,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>På gran</t>
+          <t>Rikligt på gammal lutande sälg, Rikligt med apothecier</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1905,22 +1905,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130042946</v>
+        <v>130042985</v>
       </c>
       <c r="B13" t="n">
-        <v>79095</v>
+        <v>91641</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1928,21 +1928,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1952,10 +1952,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>442870</v>
+        <v>442272</v>
       </c>
       <c r="R13" t="n">
-        <v>7006117</v>
+        <v>7005748</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1987,7 +1987,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1997,12 +1997,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>på granlåga</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2017,12 +2017,12 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -2141,10 +2141,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130042985</v>
+        <v>130042946</v>
       </c>
       <c r="B15" t="n">
-        <v>91639</v>
+        <v>79095</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2152,21 +2152,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2176,10 +2176,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>442272</v>
+        <v>442870</v>
       </c>
       <c r="R15" t="n">
-        <v>7005748</v>
+        <v>7006117</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2211,7 +2211,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2221,12 +2221,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>på granlåga</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2241,12 +2241,12 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
@@ -2368,7 +2368,7 @@
         <v>130042932</v>
       </c>
       <c r="B17" t="n">
-        <v>91635</v>
+        <v>91637</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2706,10 +2706,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130042960</v>
+        <v>130042916</v>
       </c>
       <c r="B20" t="n">
-        <v>78107</v>
+        <v>91641</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2717,21 +2717,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>228579</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2741,10 +2741,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>442328</v>
+        <v>442264</v>
       </c>
       <c r="R20" t="n">
-        <v>7005788</v>
+        <v>7005760</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2776,7 +2776,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2786,12 +2786,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>På gammal gran ca 30 cm i diameter</t>
+          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2806,22 +2806,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Ulrika Nordin, Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130042916</v>
+        <v>130042960</v>
       </c>
       <c r="B21" t="n">
-        <v>91639</v>
+        <v>78107</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2829,21 +2829,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>228579</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2853,10 +2853,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>442264</v>
+        <v>442328</v>
       </c>
       <c r="R21" t="n">
-        <v>7005760</v>
+        <v>7005788</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2888,7 +2888,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2898,12 +2898,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>På granlåga</t>
+          <t>På gammal gran ca 30 cm i diameter</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2918,44 +2918,44 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Ulrika Nordin, Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130042981</v>
+        <v>130042956</v>
       </c>
       <c r="B22" t="n">
-        <v>83073</v>
+        <v>83071</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6440</v>
+        <v>6486</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Skuggnål</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenotheca sphaerocephala</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2965,10 +2965,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>442640</v>
+        <v>442534</v>
       </c>
       <c r="R22" t="n">
-        <v>7005904</v>
+        <v>7005878</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3000,7 +3000,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3010,12 +3010,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>Vid basen av gran ca 40 cm i diameter</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3030,44 +3030,44 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Ulrika Nordin, Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130042956</v>
+        <v>130042981</v>
       </c>
       <c r="B23" t="n">
-        <v>83071</v>
+        <v>83073</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6486</v>
+        <v>6440</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Skuggnål</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Chaenotheca sphaerocephala</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3077,10 +3077,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>442534</v>
+        <v>442640</v>
       </c>
       <c r="R23" t="n">
-        <v>7005878</v>
+        <v>7005904</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3122,12 +3122,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Vid basen av gran ca 40 cm i diameter</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3142,12 +3142,12 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Ulrika Nordin, Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
@@ -3157,7 +3157,7 @@
         <v>130042934</v>
       </c>
       <c r="B24" t="n">
-        <v>91659</v>
+        <v>91661</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3262,10 +3262,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130042954</v>
+        <v>130042988</v>
       </c>
       <c r="B25" t="n">
-        <v>57741</v>
+        <v>91641</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3273,39 +3273,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Skog mellan Stenmyren och Frossjöbodarna, väster om Ågårdarna, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>442278</v>
+        <v>442709</v>
       </c>
       <c r="R25" t="n">
-        <v>7005808</v>
+        <v>7006059</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3337,7 +3332,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3347,12 +3342,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Rikligt med färska ringhack på gran ca 40 cm i diameter</t>
+          <t>på granlåga</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3367,22 +3362,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Ulrika Nordin, Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130042988</v>
+        <v>130042987</v>
       </c>
       <c r="B26" t="n">
-        <v>91639</v>
+        <v>91641</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3414,10 +3409,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>442709</v>
+        <v>442685</v>
       </c>
       <c r="R26" t="n">
-        <v>7006059</v>
+        <v>7005938</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3449,7 +3444,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3459,7 +3454,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
@@ -3491,10 +3486,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130042987</v>
+        <v>130042954</v>
       </c>
       <c r="B27" t="n">
-        <v>91639</v>
+        <v>57741</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3502,34 +3497,39 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Skog mellan Stenmyren och Frossjöbodarna, väster om Ågårdarna, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>442685</v>
+        <v>442278</v>
       </c>
       <c r="R27" t="n">
-        <v>7005938</v>
+        <v>7005808</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3561,7 +3561,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3571,12 +3571,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>på granlåga</t>
+          <t>Rikligt med färska ringhack på gran ca 40 cm i diameter</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3591,12 +3591,12 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Ulrika Nordin, Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
@@ -3606,7 +3606,7 @@
         <v>130042929</v>
       </c>
       <c r="B28" t="n">
-        <v>97702</v>
+        <v>97704</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3715,10 +3715,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130043005</v>
+        <v>130042953</v>
       </c>
       <c r="B29" t="n">
-        <v>91635</v>
+        <v>78118</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3726,21 +3726,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1108</v>
+        <v>314</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Vitskaftad svartspik</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Chaenothecopsis viridialba</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Kremp.) A.F.W.Schmidt</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3750,10 +3750,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>442514</v>
+        <v>442818</v>
       </c>
       <c r="R29" t="n">
-        <v>7005889</v>
+        <v>7006070</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3785,7 +3785,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3795,12 +3795,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>På granhögstubbe</t>
+          <t>På gammal gran ca 25 cm i diameter</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3809,28 +3809,29 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Ulrika Nordin, Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130042917</v>
+        <v>130043005</v>
       </c>
       <c r="B30" t="n">
-        <v>57741</v>
+        <v>91637</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3838,39 +3839,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Skog mellan Stenmyren och Frossjöbodarna, väster om Ågårdarna, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>442320</v>
+        <v>442514</v>
       </c>
       <c r="R30" t="n">
-        <v>7005822</v>
+        <v>7005889</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3902,7 +3898,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3912,12 +3908,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Rikligt med ringhack på 55 cm grov gammal gran</t>
+          <t>På granhögstubbe</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3932,12 +3928,12 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
@@ -4056,10 +4052,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130042953</v>
+        <v>130042917</v>
       </c>
       <c r="B32" t="n">
-        <v>78118</v>
+        <v>57741</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4067,34 +4063,39 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>314</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vitskaftad svartspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Chaenothecopsis viridialba</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Kremp.) A.F.W.Schmidt</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Skog mellan Stenmyren och Frossjöbodarna, väster om Ågårdarna, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>442818</v>
+        <v>442320</v>
       </c>
       <c r="R32" t="n">
-        <v>7006070</v>
+        <v>7005822</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4126,7 +4127,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4136,12 +4137,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>På gammal gran ca 25 cm i diameter</t>
+          <t>Rikligt med ringhack på 55 cm grov gammal gran</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4150,64 +4151,67 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Ulrika Nordin, Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>130043007</v>
+        <v>130042925</v>
       </c>
       <c r="B33" t="n">
-        <v>79095</v>
+        <v>57845</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>103031</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Skog mellan Stenmyren och Frossjöbodarna, väster om Ågårdarna, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>442871</v>
+        <v>442557</v>
       </c>
       <c r="R33" t="n">
-        <v>7006059</v>
+        <v>7005942</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4239,7 +4243,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4249,12 +4253,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>På gamla granar i gammal granskog</t>
+          <t>I gammal granskog</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4269,19 +4273,19 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130042937</v>
+        <v>130043007</v>
       </c>
       <c r="B34" t="n">
         <v>79095</v>
@@ -4316,10 +4320,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>442119</v>
+        <v>442871</v>
       </c>
       <c r="R34" t="n">
-        <v>7005573</v>
+        <v>7006059</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4351,7 +4355,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4361,12 +4365,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>På gamla granar i gammal granskog</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4381,22 +4385,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130042993</v>
+        <v>130042937</v>
       </c>
       <c r="B35" t="n">
-        <v>57741</v>
+        <v>79095</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4404,39 +4408,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Skog mellan Stenmyren och Frossjöbodarna, väster om Ågårdarna, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>442270</v>
+        <v>442119</v>
       </c>
       <c r="R35" t="n">
-        <v>7005830</v>
+        <v>7005573</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4468,7 +4467,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4478,12 +4477,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Äldre Ringhack på gran</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4498,39 +4497,39 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>130042925</v>
+        <v>130042993</v>
       </c>
       <c r="B36" t="n">
-        <v>57845</v>
+        <v>57741</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -4538,9 +4537,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>1</t>
+      <c r="I36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -4549,10 +4549,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>442557</v>
+        <v>442270</v>
       </c>
       <c r="R36" t="n">
-        <v>7005942</v>
+        <v>7005830</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4584,7 +4584,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4594,12 +4594,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>I gammal granskog</t>
+          <t>Äldre Ringhack på gran</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4614,12 +4614,12 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
@@ -4738,10 +4738,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>130042995</v>
+        <v>130042961</v>
       </c>
       <c r="B38" t="n">
-        <v>57741</v>
+        <v>91661</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4749,39 +4749,30 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Skog mellan Stenmyren och Frossjöbodarna, väster om Ågårdarna, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>442161</v>
+        <v>442177</v>
       </c>
       <c r="R38" t="n">
-        <v>7005744</v>
+        <v>7005633</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4813,7 +4804,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4823,12 +4814,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>På död gran ca 37 cm i diameter</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4843,22 +4834,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Ulrika Nordin, Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>130043001</v>
+        <v>130042935</v>
       </c>
       <c r="B39" t="n">
-        <v>83078</v>
+        <v>91661</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4866,23 +4857,19 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1467</v>
+        <v>5432</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr"/>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -4890,10 +4877,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>442691</v>
+        <v>442524</v>
       </c>
       <c r="R39" t="n">
-        <v>7005901</v>
+        <v>7005879</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4925,7 +4912,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4935,12 +4922,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>På död gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4955,22 +4942,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>130042961</v>
+        <v>130042995</v>
       </c>
       <c r="B40" t="n">
-        <v>91659</v>
+        <v>57741</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4978,30 +4965,39 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Skog mellan Stenmyren och Frossjöbodarna, väster om Ågårdarna, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>442177</v>
+        <v>442161</v>
       </c>
       <c r="R40" t="n">
-        <v>7005633</v>
+        <v>7005744</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5033,7 +5029,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5043,12 +5039,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>På död gran ca 37 cm i diameter</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5063,22 +5059,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Ulrika Nordin, Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>130042935</v>
+        <v>130043001</v>
       </c>
       <c r="B41" t="n">
-        <v>91659</v>
+        <v>83078</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5086,19 +5082,23 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5432</v>
+        <v>1467</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr"/>
+          <t>Sclerophora coniophaea</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+        </is>
+      </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>442524</v>
+        <v>442691</v>
       </c>
       <c r="R41" t="n">
-        <v>7005879</v>
+        <v>7005901</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5141,7 +5141,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>På död gran i gammal granskog</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5171,12 +5171,12 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
@@ -5410,7 +5410,7 @@
         <v>130042940</v>
       </c>
       <c r="B44" t="n">
-        <v>98735</v>
+        <v>98737</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5519,10 +5519,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>130042924</v>
+        <v>130042986</v>
       </c>
       <c r="B45" t="n">
-        <v>83078</v>
+        <v>91641</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5530,21 +5530,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1467</v>
+        <v>1202</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5554,10 +5554,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>442311</v>
+        <v>442272</v>
       </c>
       <c r="R45" t="n">
-        <v>7005788</v>
+        <v>7005763</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5589,7 +5589,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5599,12 +5599,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>På bark vid basen av gammal levande grov gran, även nordlig nållav och rostfläck och Chaenothecopsis vainioana på avverkningsstubbe under granen</t>
+          <t>på granlåga</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5619,22 +5619,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>130042986</v>
+        <v>130042924</v>
       </c>
       <c r="B46" t="n">
-        <v>91639</v>
+        <v>83078</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5642,21 +5642,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1202</v>
+        <v>1467</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5666,10 +5666,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>442272</v>
+        <v>442311</v>
       </c>
       <c r="R46" t="n">
-        <v>7005763</v>
+        <v>7005788</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5701,7 +5701,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5711,12 +5711,12 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>på granlåga</t>
+          <t>På bark vid basen av gammal levande grov gran, även nordlig nållav och rostfläck och Chaenothecopsis vainioana på avverkningsstubbe under granen</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5731,12 +5731,12 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
@@ -6087,10 +6087,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>130042983</v>
+        <v>130042991</v>
       </c>
       <c r="B50" t="n">
-        <v>83073</v>
+        <v>91641</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6098,21 +6098,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6440</v>
+        <v>1202</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6122,10 +6122,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>442821</v>
+        <v>442868</v>
       </c>
       <c r="R50" t="n">
-        <v>7006068</v>
+        <v>7006112</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6157,7 +6157,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6167,12 +6167,12 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6199,10 +6199,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>130042939</v>
+        <v>130042983</v>
       </c>
       <c r="B51" t="n">
-        <v>79095</v>
+        <v>83073</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6210,21 +6210,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6234,10 +6234,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>442182</v>
+        <v>442821</v>
       </c>
       <c r="R51" t="n">
-        <v>7005519</v>
+        <v>7006068</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6269,7 +6269,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6279,7 +6279,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
@@ -6299,22 +6299,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>130042991</v>
+        <v>130042939</v>
       </c>
       <c r="B52" t="n">
-        <v>91639</v>
+        <v>79095</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6322,21 +6322,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6346,10 +6346,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>442868</v>
+        <v>442182</v>
       </c>
       <c r="R52" t="n">
-        <v>7006112</v>
+        <v>7005519</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6381,7 +6381,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6391,12 +6391,12 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>På granlåga</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6411,12 +6411,12 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
@@ -6881,32 +6881,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>130042926</v>
+        <v>130042933</v>
       </c>
       <c r="B57" t="n">
-        <v>80201</v>
+        <v>83056</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>2081</v>
+        <v>6439</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6916,10 +6916,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>442557</v>
+        <v>442666</v>
       </c>
       <c r="R57" t="n">
-        <v>7005942</v>
+        <v>7005892</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6951,7 +6951,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6961,12 +6961,12 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>Rikligt på gammal lutande sälg i kanten av gammal granskog</t>
+          <t>På ved på grov gammal glasbjörk i gammal granskog</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6993,10 +6993,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>130042936</v>
+        <v>130042945</v>
       </c>
       <c r="B58" t="n">
-        <v>91635</v>
+        <v>79095</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7004,21 +7004,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -7028,10 +7028,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>442119</v>
+        <v>442853</v>
       </c>
       <c r="R58" t="n">
-        <v>7005573</v>
+        <v>7006058</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7063,7 +7063,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7073,12 +7073,12 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>På död gran i gammal granskog</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7105,32 +7105,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>130042933</v>
+        <v>130042931</v>
       </c>
       <c r="B59" t="n">
-        <v>83056</v>
+        <v>79095</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6439</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7140,10 +7140,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>442666</v>
+        <v>442535</v>
       </c>
       <c r="R59" t="n">
-        <v>7005892</v>
+        <v>7005862</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7175,7 +7175,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7185,12 +7185,12 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>På ved på grov gammal glasbjörk i gammal granskog</t>
+          <t>På gamla granar i gammal granskog</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7217,10 +7217,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>130042945</v>
+        <v>130042926</v>
       </c>
       <c r="B60" t="n">
-        <v>79095</v>
+        <v>80201</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7228,21 +7228,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7252,10 +7252,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>442853</v>
+        <v>442557</v>
       </c>
       <c r="R60" t="n">
-        <v>7006058</v>
+        <v>7005942</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7287,7 +7287,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>Rikligt på gammal lutande sälg i kanten av gammal granskog</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7329,10 +7329,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>130042931</v>
+        <v>130043002</v>
       </c>
       <c r="B61" t="n">
-        <v>79095</v>
+        <v>91939</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7340,21 +7340,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7364,10 +7364,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>442535</v>
+        <v>442273</v>
       </c>
       <c r="R61" t="n">
-        <v>7005862</v>
+        <v>7005747</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7399,7 +7399,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7409,12 +7409,12 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>På gamla granar i gammal granskog</t>
+          <t>på granlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7429,12 +7429,12 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
@@ -7444,7 +7444,7 @@
         <v>130042989</v>
       </c>
       <c r="B62" t="n">
-        <v>91639</v>
+        <v>91641</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7553,10 +7553,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>130043002</v>
+        <v>130042936</v>
       </c>
       <c r="B63" t="n">
-        <v>91937</v>
+        <v>91637</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7564,21 +7564,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>658</v>
+        <v>1108</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7588,10 +7588,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>442273</v>
+        <v>442119</v>
       </c>
       <c r="R63" t="n">
-        <v>7005747</v>
+        <v>7005573</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7623,7 +7623,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7633,12 +7633,12 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>på granlåga i gammal granskog</t>
+          <t>På död gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7653,12 +7653,12 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>

--- a/artfynd/A 56618-2025 artfynd.xlsx
+++ b/artfynd/A 56618-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130042928</v>
+        <v>130042984</v>
       </c>
       <c r="B2" t="n">
-        <v>78510</v>
+        <v>91728</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>502</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ladlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Calicium tigillare</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Pers.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>442500</v>
+        <v>442318</v>
       </c>
       <c r="R2" t="n">
-        <v>7005787</v>
+        <v>7005873</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,12 +755,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>På ved på gammal barrhögstubbe i gammal granskog</t>
+          <t>På gammal granlåga</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,22 +775,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130042984</v>
+        <v>130043006</v>
       </c>
       <c r="B3" t="n">
-        <v>91641</v>
+        <v>91724</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -798,21 +798,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>442318</v>
+        <v>442805</v>
       </c>
       <c r="R3" t="n">
-        <v>7005873</v>
+        <v>7006065</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,7 +857,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -867,12 +867,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>På gammal granlåga</t>
+          <t>På död gammal gran</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130043006</v>
+        <v>130042928</v>
       </c>
       <c r="B4" t="n">
-        <v>91637</v>
+        <v>78595</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -910,21 +910,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1108</v>
+        <v>502</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Ladlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Calicium tigillare</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Pers.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -934,10 +934,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>442805</v>
+        <v>442500</v>
       </c>
       <c r="R4" t="n">
-        <v>7006065</v>
+        <v>7005787</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,7 +969,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -979,12 +979,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>På död gammal gran</t>
+          <t>På ved på gammal barrhögstubbe i gammal granskog</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -999,22 +999,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130042918</v>
+        <v>130042999</v>
       </c>
       <c r="B5" t="n">
-        <v>57741</v>
+        <v>57826</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1051,10 +1051,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>442198</v>
+        <v>442253</v>
       </c>
       <c r="R5" t="n">
-        <v>7005732</v>
+        <v>7005683</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1096,12 +1096,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Färska och äldre ringhack på gammal levande grov gran i gammal granskog</t>
+          <t>Ringhack på två närliggande granar, ett färskt, ett äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1116,22 +1116,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130042999</v>
+        <v>130042918</v>
       </c>
       <c r="B6" t="n">
-        <v>57741</v>
+        <v>57826</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1168,10 +1168,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>442253</v>
+        <v>442198</v>
       </c>
       <c r="R6" t="n">
-        <v>7005683</v>
+        <v>7005732</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1203,7 +1203,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1213,12 +1213,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ringhack på två närliggande granar, ett färskt, ett äldre</t>
+          <t>Färska och äldre ringhack på gammal levande grov gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1233,12 +1233,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1248,7 +1248,7 @@
         <v>130042951</v>
       </c>
       <c r="B7" t="n">
-        <v>78107</v>
+        <v>78192</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130043003</v>
+        <v>130043004</v>
       </c>
       <c r="B8" t="n">
-        <v>78107</v>
+        <v>91724</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1368,21 +1368,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>228579</v>
+        <v>1108</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1392,10 +1392,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>442219</v>
+        <v>442160</v>
       </c>
       <c r="R8" t="n">
-        <v>7005641</v>
+        <v>7005610</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1427,7 +1427,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1437,12 +1437,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>på gammal gran i gammal granskog</t>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1469,10 +1469,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130043004</v>
+        <v>130043003</v>
       </c>
       <c r="B9" t="n">
-        <v>91637</v>
+        <v>78192</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1480,21 +1480,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1108</v>
+        <v>228579</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1504,10 +1504,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>442160</v>
+        <v>442219</v>
       </c>
       <c r="R9" t="n">
-        <v>7005610</v>
+        <v>7005641</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1539,7 +1539,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1549,12 +1549,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>På gran</t>
+          <t>på gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1584,7 +1584,7 @@
         <v>130042955</v>
       </c>
       <c r="B10" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1696,7 +1696,7 @@
         <v>130042992</v>
       </c>
       <c r="B11" t="n">
-        <v>92359</v>
+        <v>92446</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
         <v>130042927</v>
       </c>
       <c r="B12" t="n">
-        <v>80200</v>
+        <v>80285</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1917,10 +1917,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130042985</v>
+        <v>130042980</v>
       </c>
       <c r="B13" t="n">
-        <v>91641</v>
+        <v>83158</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1928,21 +1928,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>6440</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1952,10 +1952,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>442272</v>
+        <v>442510</v>
       </c>
       <c r="R13" t="n">
-        <v>7005748</v>
+        <v>7005835</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1987,7 +1987,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1997,12 +1997,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>på granlåga</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2029,10 +2029,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130042980</v>
+        <v>130042985</v>
       </c>
       <c r="B14" t="n">
-        <v>83073</v>
+        <v>91728</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2040,21 +2040,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6440</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2064,10 +2064,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>442510</v>
+        <v>442272</v>
       </c>
       <c r="R14" t="n">
-        <v>7005835</v>
+        <v>7005748</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2099,7 +2099,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2109,12 +2109,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>på granlåga</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2144,7 +2144,7 @@
         <v>130042946</v>
       </c>
       <c r="B15" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2256,7 +2256,7 @@
         <v>130042923</v>
       </c>
       <c r="B16" t="n">
-        <v>83068</v>
+        <v>83153</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2365,10 +2365,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130042932</v>
+        <v>130042996</v>
       </c>
       <c r="B17" t="n">
-        <v>91637</v>
+        <v>57826</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2376,34 +2376,39 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Skog mellan Stenmyren och Frossjöbodarna, väster om Ågårdarna, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>442535</v>
+        <v>442156</v>
       </c>
       <c r="R17" t="n">
-        <v>7005862</v>
+        <v>7005705</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2435,7 +2440,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2445,12 +2450,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>På granhögstubbe i gammal granskog</t>
+          <t>Färska och äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2465,22 +2470,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130042952</v>
+        <v>130042932</v>
       </c>
       <c r="B18" t="n">
-        <v>83073</v>
+        <v>91724</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2488,21 +2493,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6440</v>
+        <v>1108</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2512,10 +2517,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>442818</v>
+        <v>442535</v>
       </c>
       <c r="R18" t="n">
-        <v>7006070</v>
+        <v>7005862</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2547,7 +2552,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2557,12 +2562,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>På gammal gran ca 25 cm i diameter</t>
+          <t>På granhögstubbe i gammal granskog</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2577,22 +2582,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Ulrika Nordin, Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130042996</v>
+        <v>130042952</v>
       </c>
       <c r="B19" t="n">
-        <v>57741</v>
+        <v>83158</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2600,39 +2605,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Skog mellan Stenmyren och Frossjöbodarna, väster om Ågårdarna, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>442156</v>
+        <v>442818</v>
       </c>
       <c r="R19" t="n">
-        <v>7005705</v>
+        <v>7006070</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2664,7 +2664,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2674,12 +2674,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Färska och äldre ringhack på gran</t>
+          <t>På gammal gran ca 25 cm i diameter</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2694,12 +2694,12 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Ulrika Nordin, Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
@@ -2709,7 +2709,7 @@
         <v>130042916</v>
       </c>
       <c r="B20" t="n">
-        <v>91641</v>
+        <v>91728</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2821,7 +2821,7 @@
         <v>130042960</v>
       </c>
       <c r="B21" t="n">
-        <v>78107</v>
+        <v>78192</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2933,7 +2933,7 @@
         <v>130042956</v>
       </c>
       <c r="B22" t="n">
-        <v>83071</v>
+        <v>83156</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3042,10 +3042,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130042981</v>
+        <v>130042954</v>
       </c>
       <c r="B23" t="n">
-        <v>83073</v>
+        <v>57826</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3053,34 +3053,39 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Skog mellan Stenmyren och Frossjöbodarna, väster om Ågårdarna, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>442640</v>
+        <v>442278</v>
       </c>
       <c r="R23" t="n">
-        <v>7005904</v>
+        <v>7005808</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3112,7 +3117,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3122,12 +3127,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>Rikligt med färska ringhack på gran ca 40 cm i diameter</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3142,22 +3147,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Ulrika Nordin, Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130042934</v>
+        <v>130042988</v>
       </c>
       <c r="B24" t="n">
-        <v>91661</v>
+        <v>91728</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3165,19 +3170,23 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr"/>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3185,10 +3194,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>442211</v>
+        <v>442709</v>
       </c>
       <c r="R24" t="n">
-        <v>7005732</v>
+        <v>7006059</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3220,7 +3229,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3230,12 +3239,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>på granlåga</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3250,22 +3259,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130042988</v>
+        <v>130042987</v>
       </c>
       <c r="B25" t="n">
-        <v>91641</v>
+        <v>91728</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3297,10 +3306,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>442709</v>
+        <v>442685</v>
       </c>
       <c r="R25" t="n">
-        <v>7006059</v>
+        <v>7005938</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3332,7 +3341,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3342,7 +3351,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
@@ -3374,10 +3383,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130042987</v>
+        <v>130042981</v>
       </c>
       <c r="B26" t="n">
-        <v>91641</v>
+        <v>83158</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3385,21 +3394,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1202</v>
+        <v>6440</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3409,10 +3418,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>442685</v>
+        <v>442640</v>
       </c>
       <c r="R26" t="n">
-        <v>7005938</v>
+        <v>7005904</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3444,7 +3453,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3454,12 +3463,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>på granlåga</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3486,10 +3495,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130042954</v>
+        <v>130042934</v>
       </c>
       <c r="B27" t="n">
-        <v>57741</v>
+        <v>91748</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3497,39 +3506,30 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Skog mellan Stenmyren och Frossjöbodarna, väster om Ågårdarna, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>442278</v>
+        <v>442211</v>
       </c>
       <c r="R27" t="n">
-        <v>7005808</v>
+        <v>7005732</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3561,7 +3561,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3571,12 +3571,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Rikligt med färska ringhack på gran ca 40 cm i diameter</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3591,12 +3591,12 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Ulrika Nordin, Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
@@ -3606,7 +3606,7 @@
         <v>130042929</v>
       </c>
       <c r="B28" t="n">
-        <v>97704</v>
+        <v>97791</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3715,10 +3715,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130042953</v>
+        <v>130043005</v>
       </c>
       <c r="B29" t="n">
-        <v>78118</v>
+        <v>91724</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3726,21 +3726,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>314</v>
+        <v>1108</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vitskaftad svartspik</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Chaenothecopsis viridialba</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Kremp.) A.F.W.Schmidt</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3750,10 +3750,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>442818</v>
+        <v>442514</v>
       </c>
       <c r="R29" t="n">
-        <v>7006070</v>
+        <v>7005889</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3785,7 +3785,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3795,12 +3795,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>På gammal gran ca 25 cm i diameter</t>
+          <t>På granhögstubbe</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3809,29 +3809,28 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Ulrika Nordin, Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130043005</v>
+        <v>130042917</v>
       </c>
       <c r="B30" t="n">
-        <v>91637</v>
+        <v>57826</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3839,34 +3838,39 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Skog mellan Stenmyren och Frossjöbodarna, väster om Ågårdarna, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>442514</v>
+        <v>442320</v>
       </c>
       <c r="R30" t="n">
-        <v>7005889</v>
+        <v>7005822</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3898,7 +3902,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3908,12 +3912,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>På granhögstubbe</t>
+          <t>Rikligt med ringhack på 55 cm grov gammal gran</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3928,12 +3932,12 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
@@ -3943,7 +3947,7 @@
         <v>130042922</v>
       </c>
       <c r="B31" t="n">
-        <v>75073</v>
+        <v>75158</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4052,10 +4056,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130042917</v>
+        <v>130042953</v>
       </c>
       <c r="B32" t="n">
-        <v>57741</v>
+        <v>78203</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4063,39 +4067,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>314</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitskaftad svartspik</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenothecopsis viridialba</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Kremp.) A.F.W.Schmidt</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Skog mellan Stenmyren och Frossjöbodarna, väster om Ågårdarna, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>442320</v>
+        <v>442818</v>
       </c>
       <c r="R32" t="n">
-        <v>7005822</v>
+        <v>7006070</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4127,7 +4126,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4137,12 +4136,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Rikligt med ringhack på 55 cm grov gammal gran</t>
+          <t>På gammal gran ca 25 cm i diameter</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4151,67 +4150,64 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Ulrika Nordin, Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>130042925</v>
+        <v>130043007</v>
       </c>
       <c r="B33" t="n">
-        <v>57845</v>
+        <v>79180</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>103031</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Skog mellan Stenmyren och Frossjöbodarna, väster om Ågårdarna, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>442557</v>
+        <v>442871</v>
       </c>
       <c r="R33" t="n">
-        <v>7005942</v>
+        <v>7006059</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4243,7 +4239,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4253,12 +4249,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>I gammal granskog</t>
+          <t>På gamla granar i gammal granskog</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4273,22 +4269,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130043007</v>
+        <v>130042993</v>
       </c>
       <c r="B34" t="n">
-        <v>79095</v>
+        <v>57826</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4296,34 +4292,39 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Skog mellan Stenmyren och Frossjöbodarna, väster om Ågårdarna, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>442871</v>
+        <v>442270</v>
       </c>
       <c r="R34" t="n">
-        <v>7006059</v>
+        <v>7005830</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4355,7 +4356,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4365,12 +4366,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>På gamla granar i gammal granskog</t>
+          <t>Äldre Ringhack på gran</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4397,45 +4398,49 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130042937</v>
+        <v>130042925</v>
       </c>
       <c r="B35" t="n">
-        <v>79095</v>
+        <v>57930</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>103031</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Skog mellan Stenmyren och Frossjöbodarna, väster om Ågårdarna, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>442119</v>
+        <v>442557</v>
       </c>
       <c r="R35" t="n">
-        <v>7005573</v>
+        <v>7005942</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4467,7 +4472,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4477,12 +4482,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>I gammal granskog</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4509,10 +4514,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>130042993</v>
+        <v>130042937</v>
       </c>
       <c r="B36" t="n">
-        <v>57741</v>
+        <v>79180</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4520,39 +4525,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Skog mellan Stenmyren och Frossjöbodarna, väster om Ågårdarna, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>442270</v>
+        <v>442119</v>
       </c>
       <c r="R36" t="n">
-        <v>7005830</v>
+        <v>7005573</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4584,7 +4584,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4594,12 +4594,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Äldre Ringhack på gran</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4614,12 +4614,12 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
@@ -4629,7 +4629,7 @@
         <v>130042942</v>
       </c>
       <c r="B37" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4738,10 +4738,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>130042961</v>
+        <v>130042995</v>
       </c>
       <c r="B38" t="n">
-        <v>91661</v>
+        <v>57826</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4749,30 +4749,39 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Skog mellan Stenmyren och Frossjöbodarna, väster om Ågårdarna, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>442177</v>
+        <v>442161</v>
       </c>
       <c r="R38" t="n">
-        <v>7005633</v>
+        <v>7005744</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4804,7 +4813,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4814,12 +4823,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>På död gran ca 37 cm i diameter</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4834,22 +4843,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Ulrika Nordin, Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>130042935</v>
+        <v>130043001</v>
       </c>
       <c r="B39" t="n">
-        <v>91661</v>
+        <v>83163</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4857,19 +4866,23 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5432</v>
+        <v>1467</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr"/>
+          <t>Sclerophora coniophaea</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+        </is>
+      </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -4877,10 +4890,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>442524</v>
+        <v>442691</v>
       </c>
       <c r="R39" t="n">
-        <v>7005879</v>
+        <v>7005901</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4912,7 +4925,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4922,12 +4935,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>På död gran i gammal granskog</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4942,22 +4955,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>130042995</v>
+        <v>130042935</v>
       </c>
       <c r="B40" t="n">
-        <v>57741</v>
+        <v>91748</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4965,39 +4978,30 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr"/>
       <c r="I40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Skog mellan Stenmyren och Frossjöbodarna, väster om Ågårdarna, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>442161</v>
+        <v>442524</v>
       </c>
       <c r="R40" t="n">
-        <v>7005744</v>
+        <v>7005879</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5029,7 +5033,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5039,12 +5043,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>På död gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5059,22 +5063,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>130043001</v>
+        <v>130042961</v>
       </c>
       <c r="B41" t="n">
-        <v>83078</v>
+        <v>91748</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5082,23 +5086,19 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1467</v>
+        <v>5432</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>442691</v>
+        <v>442177</v>
       </c>
       <c r="R41" t="n">
-        <v>7005901</v>
+        <v>7005633</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5141,7 +5141,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>På död gran ca 37 cm i diameter</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5171,12 +5171,12 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Ulrika Nordin, Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
@@ -5186,7 +5186,7 @@
         <v>130042982</v>
       </c>
       <c r="B42" t="n">
-        <v>83073</v>
+        <v>83158</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5298,7 +5298,7 @@
         <v>130042959</v>
       </c>
       <c r="B43" t="n">
-        <v>83073</v>
+        <v>83158</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5410,7 +5410,7 @@
         <v>130042940</v>
       </c>
       <c r="B44" t="n">
-        <v>98737</v>
+        <v>98824</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5522,7 +5522,7 @@
         <v>130042986</v>
       </c>
       <c r="B45" t="n">
-        <v>91641</v>
+        <v>91728</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5631,10 +5631,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>130042924</v>
+        <v>130043008</v>
       </c>
       <c r="B46" t="n">
-        <v>83078</v>
+        <v>79180</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5642,34 +5642,43 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1467</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Skog mellan Stenmyren och Frossjöbodarna, väster om Ågårdarna, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>442311</v>
+        <v>442754</v>
       </c>
       <c r="R46" t="n">
-        <v>7005788</v>
+        <v>7006003</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5701,7 +5710,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5711,12 +5720,12 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>På bark vid basen av gammal levande grov gran, även nordlig nållav och rostfläck och Chaenothecopsis vainioana på avverkningsstubbe under granen</t>
+          <t>20 bålar på gammal gran</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5731,54 +5740,49 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>130043008</v>
+        <v>130042938</v>
       </c>
       <c r="B47" t="n">
-        <v>79095</v>
+        <v>58462</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>102125</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallbit</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pinicola enucleator</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>bålar</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
@@ -5787,10 +5791,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>442754</v>
+        <v>442182</v>
       </c>
       <c r="R47" t="n">
-        <v>7006003</v>
+        <v>7005519</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5822,7 +5826,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5832,12 +5836,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>12:44</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>20 bålar på gammal gran</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5852,22 +5851,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>130042941</v>
+        <v>130042924</v>
       </c>
       <c r="B48" t="n">
-        <v>79095</v>
+        <v>83163</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5875,21 +5874,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>1467</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5899,10 +5898,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>442223</v>
+        <v>442311</v>
       </c>
       <c r="R48" t="n">
-        <v>7005661</v>
+        <v>7005788</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5934,7 +5933,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5944,12 +5943,12 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Rikligt på gammal gran, 40 cm långa bålar</t>
+          <t>På bark vid basen av gammal levande grov gran, även nordlig nållav och rostfläck och Chaenothecopsis vainioana på avverkningsstubbe under granen</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5976,49 +5975,45 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>130042938</v>
+        <v>130042941</v>
       </c>
       <c r="B49" t="n">
-        <v>58377</v>
+        <v>79180</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>102125</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tallbit</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Pinicola enucleator</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Skog mellan Stenmyren och Frossjöbodarna, väster om Ågårdarna, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>442182</v>
+        <v>442223</v>
       </c>
       <c r="R49" t="n">
-        <v>7005519</v>
+        <v>7005661</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6050,7 +6045,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6060,7 +6055,12 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Rikligt på gammal gran, 40 cm långa bålar</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6087,10 +6087,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>130042991</v>
+        <v>130042939</v>
       </c>
       <c r="B50" t="n">
-        <v>91641</v>
+        <v>79180</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6098,21 +6098,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6122,10 +6122,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>442868</v>
+        <v>442182</v>
       </c>
       <c r="R50" t="n">
-        <v>7006112</v>
+        <v>7005519</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6157,7 +6157,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6167,12 +6167,12 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>På granlåga</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6187,12 +6187,12 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
@@ -6202,7 +6202,7 @@
         <v>130042983</v>
       </c>
       <c r="B51" t="n">
-        <v>83073</v>
+        <v>83158</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6311,10 +6311,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>130042939</v>
+        <v>130042997</v>
       </c>
       <c r="B52" t="n">
-        <v>79095</v>
+        <v>57826</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6322,34 +6322,39 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Skog mellan Stenmyren och Frossjöbodarna, väster om Ågårdarna, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>442182</v>
+        <v>442161</v>
       </c>
       <c r="R52" t="n">
-        <v>7005519</v>
+        <v>7005609</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6381,7 +6386,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6391,12 +6396,12 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>Rikligt med ringhack på gran, färska och äldre</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6411,22 +6416,22 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>130042997</v>
+        <v>130042994</v>
       </c>
       <c r="B53" t="n">
-        <v>57741</v>
+        <v>57826</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6454,7 +6459,7 @@
       <c r="I53" t="inlineStr"/>
       <c r="M53" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
@@ -6463,10 +6468,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>442161</v>
+        <v>442197</v>
       </c>
       <c r="R53" t="n">
-        <v>7005609</v>
+        <v>7005760</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6498,7 +6503,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6508,12 +6513,12 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>Rikligt med ringhack på gran, färska och äldre</t>
+          <t>Äldre Ringhack på gran</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6540,10 +6545,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>130042994</v>
+        <v>130042991</v>
       </c>
       <c r="B54" t="n">
-        <v>57741</v>
+        <v>91728</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6551,39 +6556,34 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Skog mellan Stenmyren och Frossjöbodarna, väster om Ågårdarna, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>442197</v>
+        <v>442868</v>
       </c>
       <c r="R54" t="n">
-        <v>7005760</v>
+        <v>7006112</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6615,7 +6615,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6625,12 +6625,12 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>Äldre Ringhack på gran</t>
+          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6660,7 +6660,7 @@
         <v>130042944</v>
       </c>
       <c r="B55" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6772,7 +6772,7 @@
         <v>130042943</v>
       </c>
       <c r="B56" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6881,32 +6881,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>130042933</v>
+        <v>130042926</v>
       </c>
       <c r="B57" t="n">
-        <v>83056</v>
+        <v>80286</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6439</v>
+        <v>2081</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6916,10 +6916,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>442666</v>
+        <v>442557</v>
       </c>
       <c r="R57" t="n">
-        <v>7005892</v>
+        <v>7005942</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6951,7 +6951,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6961,12 +6961,12 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>På ved på grov gammal glasbjörk i gammal granskog</t>
+          <t>Rikligt på gammal lutande sälg i kanten av gammal granskog</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6993,32 +6993,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>130042945</v>
+        <v>130042933</v>
       </c>
       <c r="B58" t="n">
-        <v>79095</v>
+        <v>83141</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>6439</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -7028,10 +7028,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>442853</v>
+        <v>442666</v>
       </c>
       <c r="R58" t="n">
-        <v>7006058</v>
+        <v>7005892</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7063,7 +7063,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7073,12 +7073,12 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>På ved på grov gammal glasbjörk i gammal granskog</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7105,10 +7105,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>130042931</v>
+        <v>130042945</v>
       </c>
       <c r="B59" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7140,10 +7140,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>442535</v>
+        <v>442853</v>
       </c>
       <c r="R59" t="n">
-        <v>7005862</v>
+        <v>7006058</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7175,7 +7175,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7185,12 +7185,12 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>På gamla granar i gammal granskog</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7217,10 +7217,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>130042926</v>
+        <v>130042931</v>
       </c>
       <c r="B60" t="n">
-        <v>80201</v>
+        <v>79180</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7228,21 +7228,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7252,10 +7252,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>442557</v>
+        <v>442535</v>
       </c>
       <c r="R60" t="n">
-        <v>7005942</v>
+        <v>7005862</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7287,7 +7287,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>Rikligt på gammal lutande sälg i kanten av gammal granskog</t>
+          <t>På gamla granar i gammal granskog</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7329,10 +7329,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>130043002</v>
+        <v>130042936</v>
       </c>
       <c r="B61" t="n">
-        <v>91939</v>
+        <v>91724</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7340,21 +7340,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>658</v>
+        <v>1108</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7364,10 +7364,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>442273</v>
+        <v>442119</v>
       </c>
       <c r="R61" t="n">
-        <v>7005747</v>
+        <v>7005573</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7399,7 +7399,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7409,12 +7409,12 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>på granlåga i gammal granskog</t>
+          <t>På död gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7429,22 +7429,22 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>130042989</v>
+        <v>130043002</v>
       </c>
       <c r="B62" t="n">
-        <v>91641</v>
+        <v>92026</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7452,21 +7452,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7476,10 +7476,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>442869</v>
+        <v>442273</v>
       </c>
       <c r="R62" t="n">
-        <v>7006064</v>
+        <v>7005747</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7511,7 +7511,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7521,12 +7521,12 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>på granlåga</t>
+          <t>på granlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7553,10 +7553,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>130042936</v>
+        <v>130042989</v>
       </c>
       <c r="B63" t="n">
-        <v>91637</v>
+        <v>91728</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7564,21 +7564,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>1108</v>
+        <v>1202</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7588,10 +7588,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>442119</v>
+        <v>442869</v>
       </c>
       <c r="R63" t="n">
-        <v>7005573</v>
+        <v>7006064</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7623,7 +7623,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7633,12 +7633,12 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>På död gran i gammal granskog</t>
+          <t>på granlåga</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7653,12 +7653,12 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
